--- a/outputs/fortress_screener.xlsx
+++ b/outputs/fortress_screener.xlsx
@@ -1329,11 +1329,11 @@
         </is>
       </c>
       <c r="BP2" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 55.0%</t>
+          <t>⚠️ MC survival 57.0%</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1534,10 +1534,10 @@
         <v>1</v>
       </c>
       <c r="EA2" t="n">
-        <v>18.89</v>
+        <v>18.93</v>
       </c>
       <c r="EB2" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="3">
@@ -1785,11 +1785,11 @@
         </is>
       </c>
       <c r="BP3" t="n">
-        <v>49.4</v>
+        <v>46.8</v>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 49.4%</t>
+          <t>⚠️ MC survival 46.8%</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1990,10 +1990,10 @@
         <v>1</v>
       </c>
       <c r="EA3" t="n">
-        <v>18.89</v>
+        <v>18.93</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="4">
@@ -2241,11 +2241,11 @@
         </is>
       </c>
       <c r="BP4" t="n">
-        <v>36.4</v>
+        <v>37</v>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 36.4%</t>
+          <t>⚠️ MC survival 37.0%</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2444,10 +2444,10 @@
         <v>1</v>
       </c>
       <c r="EA4" t="n">
-        <v>18.89</v>
+        <v>18.93</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
     </row>
   </sheetData>
@@ -3375,11 +3375,11 @@
         </is>
       </c>
       <c r="BP2" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 55.0%</t>
+          <t>⚠️ MC survival 57.0%</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -3580,10 +3580,10 @@
         <v>1</v>
       </c>
       <c r="EA2" t="n">
-        <v>18.89</v>
+        <v>18.93</v>
       </c>
       <c r="EB2" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="3">
@@ -3831,11 +3831,11 @@
         </is>
       </c>
       <c r="BP3" t="n">
-        <v>49.4</v>
+        <v>46.8</v>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 49.4%</t>
+          <t>⚠️ MC survival 46.8%</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -4036,10 +4036,10 @@
         <v>1</v>
       </c>
       <c r="EA3" t="n">
-        <v>18.89</v>
+        <v>18.93</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="4">
@@ -4287,11 +4287,11 @@
         </is>
       </c>
       <c r="BP4" t="n">
-        <v>53.2</v>
+        <v>48.4</v>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 53.2%</t>
+          <t>⚠️ MC survival 48.4%</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -4492,10 +4492,10 @@
         <v>1</v>
       </c>
       <c r="EA4" t="n">
-        <v>18.89</v>
+        <v>18.93</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="5">
@@ -4743,11 +4743,11 @@
         </is>
       </c>
       <c r="BP5" t="n">
-        <v>40.2</v>
+        <v>34.6</v>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 40.2%</t>
+          <t>⚠️ MC survival 34.6%</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -4952,10 +4952,10 @@
         <v>1</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.89</v>
+        <v>18.93</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="6">
@@ -5207,11 +5207,11 @@
         </is>
       </c>
       <c r="BP6" t="n">
-        <v>56.2</v>
+        <v>51.8</v>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 56.2%</t>
+          <t>⚠️ MC survival 51.8%</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -5416,10 +5416,10 @@
         <v>1</v>
       </c>
       <c r="EA6" t="n">
-        <v>18.89</v>
+        <v>18.93</v>
       </c>
       <c r="EB6" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="7">
@@ -5671,11 +5671,11 @@
         </is>
       </c>
       <c r="BP7" t="n">
-        <v>42</v>
+        <v>38.6</v>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 42.0%</t>
+          <t>⚠️ MC survival 38.6%</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -5874,10 +5874,10 @@
         <v>1</v>
       </c>
       <c r="EA7" t="n">
-        <v>18.89</v>
+        <v>18.93</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="8">
@@ -6125,11 +6125,11 @@
         </is>
       </c>
       <c r="BP8" t="n">
-        <v>48</v>
+        <v>50.6</v>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 48.0%</t>
+          <t>⚠️ MC survival 50.6%</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -6332,10 +6332,10 @@
         <v>1</v>
       </c>
       <c r="EA8" t="n">
-        <v>18.89</v>
+        <v>18.93</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="9">
@@ -6583,11 +6583,11 @@
         </is>
       </c>
       <c r="BP9" t="n">
-        <v>62.8</v>
+        <v>58.6</v>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 62.8%</t>
+          <t>⚠️ MC survival 58.6%</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -6790,10 +6790,10 @@
         <v>1</v>
       </c>
       <c r="EA9" t="n">
-        <v>18.89</v>
+        <v>18.93</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="10">
@@ -7045,11 +7045,11 @@
         </is>
       </c>
       <c r="BP10" t="n">
-        <v>28</v>
+        <v>29.8</v>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 28.0%</t>
+          <t>⚠️ MC survival 29.8%</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -7248,10 +7248,10 @@
         <v>1</v>
       </c>
       <c r="EA10" t="n">
-        <v>18.89</v>
+        <v>18.93</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="11">
@@ -7499,11 +7499,11 @@
         </is>
       </c>
       <c r="BP11" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 46.0%</t>
+          <t>⚠️ MC survival 45.0%</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -7702,10 +7702,10 @@
         <v>1</v>
       </c>
       <c r="EA11" t="n">
-        <v>18.89</v>
+        <v>18.93</v>
       </c>
       <c r="EB11" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="12">
@@ -7957,11 +7957,11 @@
         </is>
       </c>
       <c r="BP12" t="n">
-        <v>43.8</v>
+        <v>49.4</v>
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 43.8%</t>
+          <t>⚠️ MC survival 49.4%</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -8164,10 +8164,10 @@
         <v>1</v>
       </c>
       <c r="EA12" t="n">
-        <v>18.89</v>
+        <v>18.93</v>
       </c>
       <c r="EB12" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="13">
@@ -8415,11 +8415,11 @@
         </is>
       </c>
       <c r="BP13" t="n">
-        <v>37.8</v>
+        <v>40.8</v>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 37.8%</t>
+          <t>⚠️ MC survival 40.8%</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -8618,10 +8618,10 @@
         <v>1</v>
       </c>
       <c r="EA13" t="n">
-        <v>18.89</v>
+        <v>18.93</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="14">
@@ -8869,11 +8869,11 @@
         </is>
       </c>
       <c r="BP14" t="n">
-        <v>44.4</v>
+        <v>43.2</v>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 44.4%</t>
+          <t>⚠️ MC survival 43.2%</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -9072,10 +9072,10 @@
         <v>1</v>
       </c>
       <c r="EA14" t="n">
-        <v>18.89</v>
+        <v>18.93</v>
       </c>
       <c r="EB14" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="15">
@@ -9323,11 +9323,11 @@
         </is>
       </c>
       <c r="BP15" t="n">
-        <v>36</v>
+        <v>36.6</v>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 36.0%</t>
+          <t>⚠️ MC survival 36.6%</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -9530,10 +9530,10 @@
         <v>1</v>
       </c>
       <c r="EA15" t="n">
-        <v>18.89</v>
+        <v>18.93</v>
       </c>
       <c r="EB15" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="16">
@@ -9785,11 +9785,11 @@
         </is>
       </c>
       <c r="BP16" t="n">
-        <v>47.6</v>
+        <v>43</v>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 47.6%</t>
+          <t>⚠️ MC survival 43.0%</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -9988,10 +9988,10 @@
         <v>1</v>
       </c>
       <c r="EA16" t="n">
-        <v>18.89</v>
+        <v>18.93</v>
       </c>
       <c r="EB16" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="17">
@@ -10239,11 +10239,11 @@
         </is>
       </c>
       <c r="BP17" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 41.0%</t>
+          <t>⚠️ MC survival 42.0%</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -10442,10 +10442,10 @@
         <v>1</v>
       </c>
       <c r="EA17" t="n">
-        <v>18.89</v>
+        <v>18.93</v>
       </c>
       <c r="EB17" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="18">
@@ -10697,11 +10697,11 @@
         </is>
       </c>
       <c r="BP18" t="n">
-        <v>43.6</v>
+        <v>41.8</v>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 43.6%</t>
+          <t>⚠️ MC survival 41.8%</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -10904,10 +10904,10 @@
         <v>1</v>
       </c>
       <c r="EA18" t="n">
-        <v>18.89</v>
+        <v>18.93</v>
       </c>
       <c r="EB18" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="19">
@@ -11155,11 +11155,11 @@
         </is>
       </c>
       <c r="BP19" t="n">
-        <v>59.4</v>
+        <v>56.8</v>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 59.4%</t>
+          <t>⚠️ MC survival 56.8%</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -11364,10 +11364,10 @@
         <v>1</v>
       </c>
       <c r="EA19" t="n">
-        <v>18.89</v>
+        <v>18.93</v>
       </c>
       <c r="EB19" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="20">
@@ -11619,11 +11619,11 @@
         </is>
       </c>
       <c r="BP20" t="n">
-        <v>53</v>
+        <v>56.6</v>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 53.0%</t>
+          <t>⚠️ MC survival 56.6%</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -11826,10 +11826,10 @@
         <v>1</v>
       </c>
       <c r="EA20" t="n">
-        <v>18.89</v>
+        <v>18.93</v>
       </c>
       <c r="EB20" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="21">
@@ -11983,7 +11983,7 @@
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>No recent filing</t>
+          <t>Analysts/institutional investor meet/con. call updates [SHEETS Tab 4]</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
@@ -12077,11 +12077,11 @@
         </is>
       </c>
       <c r="BP21" t="n">
-        <v>58.8</v>
+        <v>62.2</v>
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 58.8%</t>
+          <t>⚠️ MC survival 62.2%</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -12132,7 +12132,7 @@
       </c>
       <c r="CH21" t="inlineStr">
         <is>
-          <t>Institutional tide is in — fii+dii both accumulating; recent filing: no recent filing; 2/3 fortress layers at vpoc floor</t>
+          <t>Institutional tide is in — fii+dii both accumulating; recent filing: analysts/institutional investor meet/con. call upd; 2/3 fortress layers at vpoc floor</t>
         </is>
       </c>
       <c r="CI21" t="b">
@@ -12284,10 +12284,10 @@
         <v>1</v>
       </c>
       <c r="EA21" t="n">
-        <v>18.89</v>
+        <v>18.93</v>
       </c>
       <c r="EB21" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="22">
@@ -12535,11 +12535,11 @@
         </is>
       </c>
       <c r="BP22" t="n">
-        <v>57.2</v>
+        <v>60.6</v>
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 57.2%</t>
+          <t>⚠️ MC survival 60.6%</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -12738,10 +12738,10 @@
         <v>1</v>
       </c>
       <c r="EA22" t="n">
-        <v>18.89</v>
+        <v>18.93</v>
       </c>
       <c r="EB22" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="23">
@@ -12993,11 +12993,11 @@
         </is>
       </c>
       <c r="BP23" t="n">
-        <v>41.4</v>
+        <v>39.4</v>
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 41.4%</t>
+          <t>⚠️ MC survival 39.4%</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -13200,10 +13200,10 @@
         <v>1</v>
       </c>
       <c r="EA23" t="n">
-        <v>18.89</v>
+        <v>18.93</v>
       </c>
       <c r="EB23" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="24">
@@ -13451,11 +13451,11 @@
         </is>
       </c>
       <c r="BP24" t="n">
-        <v>28.6</v>
+        <v>29.2</v>
       </c>
       <c r="BQ24" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 28.6%</t>
+          <t>⚠️ MC survival 29.2%</t>
         </is>
       </c>
       <c r="BR24" t="inlineStr">
@@ -13658,10 +13658,10 @@
         <v>1</v>
       </c>
       <c r="EA24" t="n">
-        <v>18.89</v>
+        <v>18.93</v>
       </c>
       <c r="EB24" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="25">
@@ -13913,11 +13913,11 @@
         </is>
       </c>
       <c r="BP25" t="n">
-        <v>48.6</v>
+        <v>46.4</v>
       </c>
       <c r="BQ25" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 48.6%</t>
+          <t>⚠️ MC survival 46.4%</t>
         </is>
       </c>
       <c r="BR25" t="inlineStr">
@@ -14116,10 +14116,10 @@
         <v>1</v>
       </c>
       <c r="EA25" t="n">
-        <v>18.89</v>
+        <v>18.93</v>
       </c>
       <c r="EB25" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="26">
@@ -14367,11 +14367,11 @@
         </is>
       </c>
       <c r="BP26" t="n">
-        <v>42.4</v>
+        <v>47</v>
       </c>
       <c r="BQ26" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 42.4%</t>
+          <t>⚠️ MC survival 47.0%</t>
         </is>
       </c>
       <c r="BR26" t="inlineStr">
@@ -14574,10 +14574,10 @@
         <v>1</v>
       </c>
       <c r="EA26" t="n">
-        <v>18.89</v>
+        <v>18.93</v>
       </c>
       <c r="EB26" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="27">
@@ -14825,11 +14825,11 @@
         </is>
       </c>
       <c r="BP27" t="n">
-        <v>33.2</v>
+        <v>32.8</v>
       </c>
       <c r="BQ27" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 33.2%</t>
+          <t>⚠️ MC survival 32.8%</t>
         </is>
       </c>
       <c r="BR27" t="inlineStr">
@@ -15032,10 +15032,10 @@
         <v>1</v>
       </c>
       <c r="EA27" t="n">
-        <v>18.89</v>
+        <v>18.93</v>
       </c>
       <c r="EB27" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="28">
@@ -15283,11 +15283,11 @@
         </is>
       </c>
       <c r="BP28" t="n">
-        <v>46</v>
+        <v>46.2</v>
       </c>
       <c r="BQ28" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 46.0%</t>
+          <t>⚠️ MC survival 46.2%</t>
         </is>
       </c>
       <c r="BR28" t="inlineStr">
@@ -15490,10 +15490,10 @@
         <v>1</v>
       </c>
       <c r="EA28" t="n">
-        <v>18.89</v>
+        <v>18.93</v>
       </c>
       <c r="EB28" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="29">
@@ -15741,11 +15741,11 @@
         </is>
       </c>
       <c r="BP29" t="n">
-        <v>49.2</v>
+        <v>48</v>
       </c>
       <c r="BQ29" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 49.2%</t>
+          <t>⚠️ MC survival 48.0%</t>
         </is>
       </c>
       <c r="BR29" t="inlineStr">
@@ -15948,10 +15948,10 @@
         <v>1</v>
       </c>
       <c r="EA29" t="n">
-        <v>18.89</v>
+        <v>18.93</v>
       </c>
       <c r="EB29" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="30">
@@ -16203,11 +16203,11 @@
         </is>
       </c>
       <c r="BP30" t="n">
-        <v>61.2</v>
+        <v>57.2</v>
       </c>
       <c r="BQ30" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 61.2%</t>
+          <t>⚠️ MC survival 57.2%</t>
         </is>
       </c>
       <c r="BR30" t="inlineStr">
@@ -16406,10 +16406,10 @@
         <v>1</v>
       </c>
       <c r="EA30" t="n">
-        <v>18.89</v>
+        <v>18.93</v>
       </c>
       <c r="EB30" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="31">
@@ -16657,11 +16657,11 @@
         </is>
       </c>
       <c r="BP31" t="n">
-        <v>51.4</v>
+        <v>53.6</v>
       </c>
       <c r="BQ31" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 51.4%</t>
+          <t>⚠️ MC survival 53.6%</t>
         </is>
       </c>
       <c r="BR31" t="inlineStr">
@@ -16860,10 +16860,10 @@
         <v>1</v>
       </c>
       <c r="EA31" t="n">
-        <v>18.89</v>
+        <v>18.93</v>
       </c>
       <c r="EB31" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="32">
@@ -17111,11 +17111,11 @@
         </is>
       </c>
       <c r="BP32" t="n">
-        <v>42.6</v>
+        <v>43.4</v>
       </c>
       <c r="BQ32" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 42.6%</t>
+          <t>⚠️ MC survival 43.4%</t>
         </is>
       </c>
       <c r="BR32" t="inlineStr">
@@ -17314,10 +17314,10 @@
         <v>1</v>
       </c>
       <c r="EA32" t="n">
-        <v>18.89</v>
+        <v>18.93</v>
       </c>
       <c r="EB32" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="33">
@@ -17565,11 +17565,11 @@
         </is>
       </c>
       <c r="BP33" t="n">
-        <v>37.4</v>
+        <v>34.8</v>
       </c>
       <c r="BQ33" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 37.4%</t>
+          <t>⚠️ MC survival 34.8%</t>
         </is>
       </c>
       <c r="BR33" t="inlineStr">
@@ -17768,10 +17768,10 @@
         <v>1</v>
       </c>
       <c r="EA33" t="n">
-        <v>18.89</v>
+        <v>18.93</v>
       </c>
       <c r="EB33" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="34">
@@ -18019,11 +18019,11 @@
         </is>
       </c>
       <c r="BP34" t="n">
-        <v>32.4</v>
+        <v>34.2</v>
       </c>
       <c r="BQ34" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 32.4%</t>
+          <t>⚠️ MC survival 34.2%</t>
         </is>
       </c>
       <c r="BR34" t="inlineStr">
@@ -18222,10 +18222,10 @@
         <v>1</v>
       </c>
       <c r="EA34" t="n">
-        <v>18.89</v>
+        <v>18.93</v>
       </c>
       <c r="EB34" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="35">
@@ -18477,11 +18477,11 @@
         </is>
       </c>
       <c r="BP35" t="n">
-        <v>33.2</v>
+        <v>32.2</v>
       </c>
       <c r="BQ35" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 33.2%</t>
+          <t>⚠️ MC survival 32.2%</t>
         </is>
       </c>
       <c r="BR35" t="inlineStr">
@@ -18680,10 +18680,10 @@
         <v>1</v>
       </c>
       <c r="EA35" t="n">
-        <v>18.89</v>
+        <v>18.93</v>
       </c>
       <c r="EB35" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="36">
@@ -18935,11 +18935,11 @@
         </is>
       </c>
       <c r="BP36" t="n">
-        <v>31.8</v>
+        <v>29.8</v>
       </c>
       <c r="BQ36" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 31.8%</t>
+          <t>⚠️ MC survival 29.8%</t>
         </is>
       </c>
       <c r="BR36" t="inlineStr">
@@ -19138,10 +19138,10 @@
         <v>1</v>
       </c>
       <c r="EA36" t="n">
-        <v>18.89</v>
+        <v>18.93</v>
       </c>
       <c r="EB36" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="37">
@@ -19393,11 +19393,11 @@
         </is>
       </c>
       <c r="BP37" t="n">
-        <v>25</v>
+        <v>23.2</v>
       </c>
       <c r="BQ37" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 25.0%</t>
+          <t>⚠️ MC survival 23.2%</t>
         </is>
       </c>
       <c r="BR37" t="inlineStr">
@@ -19596,10 +19596,10 @@
         <v>1</v>
       </c>
       <c r="EA37" t="n">
-        <v>18.89</v>
+        <v>18.93</v>
       </c>
       <c r="EB37" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="38">
@@ -19847,11 +19847,11 @@
         </is>
       </c>
       <c r="BP38" t="n">
-        <v>42</v>
+        <v>43.6</v>
       </c>
       <c r="BQ38" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 42.0%</t>
+          <t>⚠️ MC survival 43.6%</t>
         </is>
       </c>
       <c r="BR38" t="inlineStr">
@@ -20050,10 +20050,10 @@
         <v>1</v>
       </c>
       <c r="EA38" t="n">
-        <v>18.89</v>
+        <v>18.93</v>
       </c>
       <c r="EB38" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="39">
@@ -20305,11 +20305,11 @@
         </is>
       </c>
       <c r="BP39" t="n">
-        <v>49.2</v>
+        <v>43.6</v>
       </c>
       <c r="BQ39" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 49.2%</t>
+          <t>⚠️ MC survival 43.6%</t>
         </is>
       </c>
       <c r="BR39" t="inlineStr">
@@ -20508,10 +20508,10 @@
         <v>1</v>
       </c>
       <c r="EA39" t="n">
-        <v>18.89</v>
+        <v>18.93</v>
       </c>
       <c r="EB39" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="40">
@@ -20759,11 +20759,11 @@
         </is>
       </c>
       <c r="BP40" t="n">
-        <v>69.40000000000001</v>
+        <v>67</v>
       </c>
       <c r="BQ40" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 69.4%</t>
+          <t>⚠️ MC survival 67.0%</t>
         </is>
       </c>
       <c r="BR40" t="inlineStr">
@@ -20966,10 +20966,10 @@
         <v>1</v>
       </c>
       <c r="EA40" t="n">
-        <v>18.89</v>
+        <v>18.93</v>
       </c>
       <c r="EB40" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="41">
@@ -21217,11 +21217,11 @@
         </is>
       </c>
       <c r="BP41" t="n">
-        <v>67.8</v>
+        <v>67.2</v>
       </c>
       <c r="BQ41" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 67.8%</t>
+          <t>⚠️ MC survival 67.2%</t>
         </is>
       </c>
       <c r="BR41" t="inlineStr">
@@ -21420,10 +21420,10 @@
         <v>1</v>
       </c>
       <c r="EA41" t="n">
-        <v>18.89</v>
+        <v>18.93</v>
       </c>
       <c r="EB41" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="42">
@@ -21671,11 +21671,11 @@
         </is>
       </c>
       <c r="BP42" t="n">
-        <v>29</v>
+        <v>27.4</v>
       </c>
       <c r="BQ42" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 29.0%</t>
+          <t>⚠️ MC survival 27.4%</t>
         </is>
       </c>
       <c r="BR42" t="inlineStr">
@@ -21874,10 +21874,10 @@
         <v>1</v>
       </c>
       <c r="EA42" t="n">
-        <v>18.89</v>
+        <v>18.93</v>
       </c>
       <c r="EB42" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="43">
@@ -22125,11 +22125,11 @@
         </is>
       </c>
       <c r="BP43" t="n">
-        <v>63.8</v>
+        <v>63.2</v>
       </c>
       <c r="BQ43" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 63.8%</t>
+          <t>⚠️ MC survival 63.2%</t>
         </is>
       </c>
       <c r="BR43" t="inlineStr">
@@ -22328,10 +22328,10 @@
         <v>1</v>
       </c>
       <c r="EA43" t="n">
-        <v>18.89</v>
+        <v>18.93</v>
       </c>
       <c r="EB43" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="44">
@@ -22583,11 +22583,11 @@
         </is>
       </c>
       <c r="BP44" t="n">
-        <v>35.2</v>
+        <v>36.6</v>
       </c>
       <c r="BQ44" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 35.2%</t>
+          <t>⚠️ MC survival 36.6%</t>
         </is>
       </c>
       <c r="BR44" t="inlineStr">
@@ -22786,10 +22786,10 @@
         <v>1</v>
       </c>
       <c r="EA44" t="n">
-        <v>18.89</v>
+        <v>18.93</v>
       </c>
       <c r="EB44" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="45">
@@ -23037,11 +23037,11 @@
         </is>
       </c>
       <c r="BP45" t="n">
-        <v>45.4</v>
+        <v>46.2</v>
       </c>
       <c r="BQ45" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 45.4%</t>
+          <t>⚠️ MC survival 46.2%</t>
         </is>
       </c>
       <c r="BR45" t="inlineStr">
@@ -23240,10 +23240,10 @@
         <v>1</v>
       </c>
       <c r="EA45" t="n">
-        <v>18.89</v>
+        <v>18.93</v>
       </c>
       <c r="EB45" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="46">
@@ -23491,11 +23491,11 @@
         </is>
       </c>
       <c r="BP46" t="n">
-        <v>40.8</v>
+        <v>37.6</v>
       </c>
       <c r="BQ46" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 40.8%</t>
+          <t>⚠️ MC survival 37.6%</t>
         </is>
       </c>
       <c r="BR46" t="inlineStr">
@@ -23694,10 +23694,10 @@
         <v>1</v>
       </c>
       <c r="EA46" t="n">
-        <v>18.89</v>
+        <v>18.93</v>
       </c>
       <c r="EB46" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="47">
@@ -23945,11 +23945,11 @@
         </is>
       </c>
       <c r="BP47" t="n">
-        <v>62.2</v>
+        <v>60</v>
       </c>
       <c r="BQ47" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 62.2%</t>
+          <t>⚠️ MC survival 60.0%</t>
         </is>
       </c>
       <c r="BR47" t="inlineStr">
@@ -24148,10 +24148,10 @@
         <v>1</v>
       </c>
       <c r="EA47" t="n">
-        <v>18.89</v>
+        <v>18.93</v>
       </c>
       <c r="EB47" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="48">
@@ -24399,11 +24399,11 @@
         </is>
       </c>
       <c r="BP48" t="n">
-        <v>28.2</v>
+        <v>31.4</v>
       </c>
       <c r="BQ48" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 28.2%</t>
+          <t>⚠️ MC survival 31.4%</t>
         </is>
       </c>
       <c r="BR48" t="inlineStr">
@@ -24606,10 +24606,10 @@
         <v>1</v>
       </c>
       <c r="EA48" t="n">
-        <v>18.89</v>
+        <v>18.93</v>
       </c>
       <c r="EB48" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="49">
@@ -24857,11 +24857,11 @@
         </is>
       </c>
       <c r="BP49" t="n">
-        <v>66.40000000000001</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="BQ49" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 66.4%</t>
+          <t>⚠️ MC survival 64.6%</t>
         </is>
       </c>
       <c r="BR49" t="inlineStr">
@@ -25064,10 +25064,10 @@
         <v>1</v>
       </c>
       <c r="EA49" t="n">
-        <v>18.89</v>
+        <v>18.93</v>
       </c>
       <c r="EB49" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="50">
@@ -25315,11 +25315,11 @@
         </is>
       </c>
       <c r="BP50" t="n">
-        <v>50</v>
+        <v>47.6</v>
       </c>
       <c r="BQ50" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 50.0%</t>
+          <t>⚠️ MC survival 47.6%</t>
         </is>
       </c>
       <c r="BR50" t="inlineStr">
@@ -25518,10 +25518,10 @@
         <v>1</v>
       </c>
       <c r="EA50" t="n">
-        <v>18.89</v>
+        <v>18.93</v>
       </c>
       <c r="EB50" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="51">
@@ -25769,11 +25769,11 @@
         </is>
       </c>
       <c r="BP51" t="n">
-        <v>42.8</v>
+        <v>48</v>
       </c>
       <c r="BQ51" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 42.8%</t>
+          <t>⚠️ MC survival 48.0%</t>
         </is>
       </c>
       <c r="BR51" t="inlineStr">
@@ -25976,10 +25976,10 @@
         <v>1</v>
       </c>
       <c r="EA51" t="n">
-        <v>18.89</v>
+        <v>18.93</v>
       </c>
       <c r="EB51" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="52">
@@ -26231,11 +26231,11 @@
         </is>
       </c>
       <c r="BP52" t="n">
-        <v>24.8</v>
+        <v>26.8</v>
       </c>
       <c r="BQ52" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 24.8%</t>
+          <t>⚠️ MC survival 26.8%</t>
         </is>
       </c>
       <c r="BR52" t="inlineStr">
@@ -26434,10 +26434,10 @@
         <v>1</v>
       </c>
       <c r="EA52" t="n">
-        <v>18.89</v>
+        <v>18.93</v>
       </c>
       <c r="EB52" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="53">
@@ -26685,11 +26685,11 @@
         </is>
       </c>
       <c r="BP53" t="n">
-        <v>36.8</v>
+        <v>35.2</v>
       </c>
       <c r="BQ53" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 36.8%</t>
+          <t>⚠️ MC survival 35.2%</t>
         </is>
       </c>
       <c r="BR53" t="inlineStr">
@@ -26888,10 +26888,10 @@
         <v>1</v>
       </c>
       <c r="EA53" t="n">
-        <v>18.89</v>
+        <v>18.93</v>
       </c>
       <c r="EB53" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="54">
@@ -27139,11 +27139,11 @@
         </is>
       </c>
       <c r="BP54" t="n">
-        <v>35.8</v>
+        <v>35.4</v>
       </c>
       <c r="BQ54" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 35.8%</t>
+          <t>⚠️ MC survival 35.4%</t>
         </is>
       </c>
       <c r="BR54" t="inlineStr">
@@ -27342,10 +27342,10 @@
         <v>1</v>
       </c>
       <c r="EA54" t="n">
-        <v>18.89</v>
+        <v>18.93</v>
       </c>
       <c r="EB54" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="55">
@@ -27593,11 +27593,11 @@
         </is>
       </c>
       <c r="BP55" t="n">
-        <v>64</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="BQ55" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 64.0%</t>
+          <t>⚠️ MC survival 64.4%</t>
         </is>
       </c>
       <c r="BR55" t="inlineStr">
@@ -27796,10 +27796,10 @@
         <v>1</v>
       </c>
       <c r="EA55" t="n">
-        <v>18.89</v>
+        <v>18.93</v>
       </c>
       <c r="EB55" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="56">
@@ -28047,11 +28047,11 @@
         </is>
       </c>
       <c r="BP56" t="n">
-        <v>28.4</v>
+        <v>26.2</v>
       </c>
       <c r="BQ56" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 28.4%</t>
+          <t>⚠️ MC survival 26.2%</t>
         </is>
       </c>
       <c r="BR56" t="inlineStr">
@@ -28250,10 +28250,10 @@
         <v>1</v>
       </c>
       <c r="EA56" t="n">
-        <v>18.89</v>
+        <v>18.93</v>
       </c>
       <c r="EB56" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="57">
@@ -28505,11 +28505,11 @@
         </is>
       </c>
       <c r="BP57" t="n">
-        <v>31.4</v>
+        <v>34.4</v>
       </c>
       <c r="BQ57" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 31.4%</t>
+          <t>⚠️ MC survival 34.4%</t>
         </is>
       </c>
       <c r="BR57" t="inlineStr">
@@ -28708,10 +28708,10 @@
         <v>1</v>
       </c>
       <c r="EA57" t="n">
-        <v>18.89</v>
+        <v>18.93</v>
       </c>
       <c r="EB57" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="58">
@@ -28959,11 +28959,11 @@
         </is>
       </c>
       <c r="BP58" t="n">
-        <v>32.2</v>
+        <v>30</v>
       </c>
       <c r="BQ58" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 32.2%</t>
+          <t>⚠️ MC survival 30.0%</t>
         </is>
       </c>
       <c r="BR58" t="inlineStr">
@@ -29162,10 +29162,10 @@
         <v>1</v>
       </c>
       <c r="EA58" t="n">
-        <v>18.89</v>
+        <v>18.93</v>
       </c>
       <c r="EB58" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="59">
@@ -29413,11 +29413,11 @@
         </is>
       </c>
       <c r="BP59" t="n">
-        <v>36.4</v>
+        <v>37</v>
       </c>
       <c r="BQ59" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 36.4%</t>
+          <t>⚠️ MC survival 37.0%</t>
         </is>
       </c>
       <c r="BR59" t="inlineStr">
@@ -29616,10 +29616,10 @@
         <v>1</v>
       </c>
       <c r="EA59" t="n">
-        <v>18.89</v>
+        <v>18.93</v>
       </c>
       <c r="EB59" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="60">
@@ -29871,11 +29871,11 @@
         </is>
       </c>
       <c r="BP60" t="n">
-        <v>68</v>
+        <v>65.8</v>
       </c>
       <c r="BQ60" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 68.0%</t>
+          <t>⚠️ MC survival 65.8%</t>
         </is>
       </c>
       <c r="BR60" t="inlineStr">
@@ -30078,10 +30078,10 @@
         <v>1</v>
       </c>
       <c r="EA60" t="n">
-        <v>18.89</v>
+        <v>18.93</v>
       </c>
       <c r="EB60" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="61">
@@ -30329,11 +30329,11 @@
         </is>
       </c>
       <c r="BP61" t="n">
-        <v>66.40000000000001</v>
+        <v>66.8</v>
       </c>
       <c r="BQ61" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 66.4%</t>
+          <t>⚠️ MC survival 66.8%</t>
         </is>
       </c>
       <c r="BR61" t="inlineStr">
@@ -30532,10 +30532,10 @@
         <v>1</v>
       </c>
       <c r="EA61" t="n">
-        <v>18.89</v>
+        <v>18.93</v>
       </c>
       <c r="EB61" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/fortress_screener.xlsx
+++ b/outputs/fortress_screener.xlsx
@@ -1100,7 +1100,7 @@
         <v>271.75</v>
       </c>
       <c r="D2" t="n">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="E2" t="n">
         <v>200</v>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="I2" t="n">
         <v>30</v>
@@ -1273,17 +1273,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>🌀 VDU 5-bar deep coil (+7pts)</t>
+          <t>🔴 VDU 5-bar + price drop -3.7% — DISTRIBUTION (-3pts)</t>
         </is>
       </c>
       <c r="AY2" t="n">
-        <v>7</v>
+        <v>-3</v>
       </c>
       <c r="AZ2" t="n">
         <v>5</v>
       </c>
       <c r="BA2" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="BB2" t="inlineStr"/>
       <c r="BC2" t="n">
@@ -1337,11 +1337,11 @@
         </is>
       </c>
       <c r="BQ2" t="n">
-        <v>30.2</v>
+        <v>35</v>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 30.2% (t(df=4))</t>
+          <t>⚠️ MC survival 35.0% (t(df=4))</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1542,10 +1542,10 @@
         <v>1</v>
       </c>
       <c r="EB2" t="n">
-        <v>18.58</v>
+        <v>18.41</v>
       </c>
       <c r="EC2" t="n">
-        <v>0.01</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="3">
@@ -1563,7 +1563,7 @@
         <v>520.4</v>
       </c>
       <c r="D3" t="n">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="E3" t="n">
         <v>200</v>
@@ -1579,7 +1579,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="I3" t="n">
         <v>30</v>
@@ -1736,17 +1736,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>🌀 VDU 3-bar mild (+3pts)</t>
+          <t>🔴 VDU 3-bar + price drop -5.4% — DISTRIBUTION (-3pts)</t>
         </is>
       </c>
       <c r="AY3" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="AZ3" t="n">
         <v>3</v>
       </c>
       <c r="BA3" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="BB3" t="inlineStr"/>
       <c r="BC3" t="n">
@@ -1800,11 +1800,11 @@
         </is>
       </c>
       <c r="BQ3" t="n">
-        <v>52.8</v>
+        <v>56.6</v>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 52.8% (t(df=4))</t>
+          <t>⚠️ MC survival 56.6% (t(df=4))</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -2009,10 +2009,10 @@
         <v>1</v>
       </c>
       <c r="EB3" t="n">
-        <v>18.58</v>
+        <v>18.41</v>
       </c>
       <c r="EC3" t="n">
-        <v>0.01</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="4">
@@ -2067,7 +2067,7 @@
         <v>97.05</v>
       </c>
       <c r="O4" t="n">
-        <v>91.29000000000001</v>
+        <v>90.91</v>
       </c>
       <c r="P4" t="n">
         <v>101.88</v>
@@ -2079,10 +2079,10 @@
         <v>156.74</v>
       </c>
       <c r="S4" t="n">
-        <v>2.06</v>
+        <v>2.47</v>
       </c>
       <c r="T4" t="n">
-        <v>7.28</v>
+        <v>6.08</v>
       </c>
       <c r="U4" t="n">
         <v>69</v>
@@ -2120,11 +2120,11 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ATR-0.75× stop</t>
+          <t>ATR-0.90× stop</t>
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="AE4" t="n">
         <v>18.68</v>
@@ -2230,25 +2230,25 @@
         </is>
       </c>
       <c r="BH4" t="n">
-        <v>91.29000000000001</v>
+        <v>90.91</v>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>Initial stop ₹91.29</t>
+          <t>Initial stop ₹90.91</t>
         </is>
       </c>
       <c r="BJ4" t="b">
         <v>0</v>
       </c>
       <c r="BK4" t="n">
-        <v>3906</v>
+        <v>3255</v>
       </c>
       <c r="BL4" t="n">
-        <v>364078.26</v>
+        <v>303398.55</v>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>3906 shares · ₹364,078  (risk ₹7,500)</t>
+          <t>3255 shares · ₹303,399  (risk ₹7,500)</t>
         </is>
       </c>
       <c r="BN4" t="n">
@@ -2263,11 +2263,11 @@
         </is>
       </c>
       <c r="BQ4" t="n">
-        <v>39.8</v>
+        <v>45.8</v>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 39.8% (t(df=4))</t>
+          <t>⚠️ MC survival 45.8% (t(df=4))</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2379,10 +2379,10 @@
         <v>1</v>
       </c>
       <c r="DC4" t="n">
-        <v>91.29000000000001</v>
+        <v>90.91</v>
       </c>
       <c r="DD4" t="n">
-        <v>91.29000000000001</v>
+        <v>90.91</v>
       </c>
       <c r="DE4" t="n">
         <v>101.88</v>
@@ -2466,10 +2466,10 @@
         <v>1</v>
       </c>
       <c r="EB4" t="n">
-        <v>18.58</v>
+        <v>18.41</v>
       </c>
       <c r="EC4" t="n">
-        <v>0.01</v>
+        <v>0.45</v>
       </c>
     </row>
   </sheetData>
@@ -3168,7 +3168,7 @@
         <v>271.75</v>
       </c>
       <c r="D2" t="n">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="E2" t="n">
         <v>200</v>
@@ -3184,7 +3184,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="I2" t="n">
         <v>30</v>
@@ -3341,17 +3341,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>🌀 VDU 5-bar deep coil (+7pts)</t>
+          <t>🔴 VDU 5-bar + price drop -3.7% — DISTRIBUTION (-3pts)</t>
         </is>
       </c>
       <c r="AY2" t="n">
-        <v>7</v>
+        <v>-3</v>
       </c>
       <c r="AZ2" t="n">
         <v>5</v>
       </c>
       <c r="BA2" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="BB2" t="inlineStr"/>
       <c r="BC2" t="n">
@@ -3405,11 +3405,11 @@
         </is>
       </c>
       <c r="BQ2" t="n">
-        <v>30.2</v>
+        <v>35</v>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 30.2% (t(df=4))</t>
+          <t>⚠️ MC survival 35.0% (t(df=4))</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -3610,10 +3610,10 @@
         <v>1</v>
       </c>
       <c r="EB2" t="n">
-        <v>18.58</v>
+        <v>18.41</v>
       </c>
       <c r="EC2" t="n">
-        <v>0.01</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="3">
@@ -3631,7 +3631,7 @@
         <v>520.4</v>
       </c>
       <c r="D3" t="n">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="E3" t="n">
         <v>200</v>
@@ -3647,7 +3647,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="I3" t="n">
         <v>30</v>
@@ -3804,17 +3804,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>🌀 VDU 3-bar mild (+3pts)</t>
+          <t>🔴 VDU 3-bar + price drop -5.4% — DISTRIBUTION (-3pts)</t>
         </is>
       </c>
       <c r="AY3" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="AZ3" t="n">
         <v>3</v>
       </c>
       <c r="BA3" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="BB3" t="inlineStr"/>
       <c r="BC3" t="n">
@@ -3868,11 +3868,11 @@
         </is>
       </c>
       <c r="BQ3" t="n">
-        <v>52.8</v>
+        <v>56.6</v>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 52.8% (t(df=4))</t>
+          <t>⚠️ MC survival 56.6% (t(df=4))</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -4077,10 +4077,10 @@
         <v>1</v>
       </c>
       <c r="EB3" t="n">
-        <v>18.58</v>
+        <v>18.41</v>
       </c>
       <c r="EC3" t="n">
-        <v>0.01</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="4">
@@ -4098,7 +4098,7 @@
         <v>383.75</v>
       </c>
       <c r="D4" t="n">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="E4" t="n">
         <v>200</v>
@@ -4114,7 +4114,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="I4" t="n">
         <v>30</v>
@@ -4271,17 +4271,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>🌀 VDU 5-bar deep coil (+7pts)</t>
+          <t>🔴 VDU 5-bar + price drop -8.1% — DISTRIBUTION (-3pts)</t>
         </is>
       </c>
       <c r="AY4" t="n">
-        <v>7</v>
+        <v>-3</v>
       </c>
       <c r="AZ4" t="n">
         <v>5</v>
       </c>
       <c r="BA4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BB4" t="inlineStr"/>
       <c r="BC4" t="n">
@@ -4335,11 +4335,11 @@
         </is>
       </c>
       <c r="BQ4" t="n">
-        <v>55</v>
+        <v>59.6</v>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 55.0% (t(df=4))</t>
+          <t>⚠️ MC survival 59.6% (t(df=4))</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -4544,10 +4544,10 @@
         <v>1</v>
       </c>
       <c r="EB4" t="n">
-        <v>18.58</v>
+        <v>18.41</v>
       </c>
       <c r="EC4" t="n">
-        <v>0.01</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="5">
@@ -4802,11 +4802,11 @@
         </is>
       </c>
       <c r="BQ5" t="n">
-        <v>27</v>
+        <v>24.8</v>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 27.0% (t(df=4))</t>
+          <t>⚠️ MC survival 24.8% (t(df=4))</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -5007,10 +5007,10 @@
         <v>1</v>
       </c>
       <c r="EB5" t="n">
-        <v>18.58</v>
+        <v>18.41</v>
       </c>
       <c r="EC5" t="n">
-        <v>0.01</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="6">
@@ -5261,11 +5261,11 @@
         </is>
       </c>
       <c r="BQ6" t="n">
-        <v>23.2</v>
+        <v>23.8</v>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 23.2% (t(df=4))</t>
+          <t>⚠️ MC survival 23.8% (t(df=4))</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -5466,10 +5466,10 @@
         <v>1</v>
       </c>
       <c r="EB6" t="n">
-        <v>18.58</v>
+        <v>18.41</v>
       </c>
       <c r="EC6" t="n">
-        <v>0.01</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="7">
@@ -5724,11 +5724,11 @@
         </is>
       </c>
       <c r="BQ7" t="n">
-        <v>54.8</v>
+        <v>55.6</v>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 54.8% (t(df=4))</t>
+          <t>⚠️ MC survival 55.6% (t(df=4))</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -5929,16 +5929,16 @@
         <v>1</v>
       </c>
       <c r="EB7" t="n">
-        <v>18.58</v>
+        <v>18.41</v>
       </c>
       <c r="EC7" t="n">
-        <v>0.01</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CONCOR</t>
+          <t>MONARCH</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -5947,7 +5947,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>522.95</v>
+        <v>308.4</v>
       </c>
       <c r="D8" t="n">
         <v>135</v>
@@ -5966,7 +5966,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="I8" t="n">
         <v>30</v>
@@ -5978,40 +5978,40 @@
         <v>15</v>
       </c>
       <c r="L8" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="M8" t="n">
-        <v>513.27</v>
+        <v>306.51</v>
       </c>
       <c r="N8" t="n">
-        <v>539.59</v>
+        <v>325.59</v>
       </c>
       <c r="O8" t="n">
-        <v>507.42</v>
+        <v>292.36</v>
       </c>
       <c r="P8" t="n">
-        <v>667.25</v>
+        <v>398.46</v>
       </c>
       <c r="Q8" t="n">
-        <v>821.23</v>
+        <v>490.42</v>
       </c>
       <c r="R8" t="n">
-        <v>1026.54</v>
+        <v>613.02</v>
       </c>
       <c r="S8" t="n">
-        <v>2.97</v>
+        <v>5.2</v>
       </c>
       <c r="T8" t="n">
-        <v>5.05</v>
+        <v>2.88</v>
       </c>
       <c r="U8" t="n">
-        <v>58.8</v>
+        <v>62.1</v>
       </c>
       <c r="V8" t="n">
-        <v>57.7</v>
+        <v>59.9</v>
       </c>
       <c r="W8" t="n">
-        <v>46.8</v>
+        <v>30</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -6025,7 +6025,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>NEUTRAL ↔</t>
+          <t>DISTRIBUTION 🔴</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -6035,7 +6035,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>₹504.56–₹523.85</t>
+          <t>₹297.40–₹315.27</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -6047,7 +6047,7 @@
         <v>1.4</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.08</v>
+        <v>0.83</v>
       </c>
       <c r="AF8" t="b">
         <v>1</v>
@@ -6062,7 +6062,7 @@
         <v>1</v>
       </c>
       <c r="AJ8" t="n">
-        <v>37.44</v>
+        <v>5.03</v>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
@@ -6089,12 +6089,12 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>General updates [SHEETS Tab 4]</t>
+          <t>No recent filing</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>Results in 7td — caution</t>
+          <t>Results just 1td ago — fresh data</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
@@ -6107,7 +6107,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>52W: 19.8% from ₹652 [20% from 52W high] +0pts</t>
+          <t>52W: 22.7% from ₹399 [23% from 52W high] +0pts</t>
         </is>
       </c>
       <c r="AU8" t="n">
@@ -6115,29 +6115,29 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>ATR-V: 9% compressed [🌀 COILING (+4pts)]</t>
+          <t>ATR-V: -6% compressed [EXPANDING]</t>
         </is>
       </c>
       <c r="AW8" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>🌀 VDU 3-bar mild (+3pts)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AX8" t="inlineStr"/>
       <c r="AY8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AZ8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB8" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>🔥 HOT PEAD — 4.8% drift 1td post-results (+10pts)</t>
+        </is>
+      </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -6154,25 +6154,25 @@
         </is>
       </c>
       <c r="BH8" t="n">
-        <v>507.42</v>
+        <v>292.36</v>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>Initial stop ₹507.42</t>
+          <t>Initial stop ₹292.36</t>
         </is>
       </c>
       <c r="BJ8" t="b">
         <v>0</v>
       </c>
       <c r="BK8" t="n">
-        <v>483</v>
+        <v>467</v>
       </c>
       <c r="BL8" t="n">
-        <v>252584.85</v>
+        <v>144022.8</v>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>483 shares · ₹252,585  (risk ₹7,500)</t>
+          <t>467 shares · ₹144,023  (risk ₹7,500)</t>
         </is>
       </c>
       <c r="BN8" t="n">
@@ -6187,19 +6187,23 @@
         </is>
       </c>
       <c r="BQ8" t="n">
-        <v>42</v>
+        <v>58.8</v>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 42.0% (t(df=4))</t>
+          <t>⚠️ MC survival 58.8% (t(df=4))</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="BT8" t="inlineStr"/>
+          <t>DISTRIBUTION</t>
+        </is>
+      </c>
+      <c r="BT8" t="inlineStr">
+        <is>
+          <t>🔴 CVD Diverge — distribution</t>
+        </is>
+      </c>
       <c r="BU8" t="b">
         <v>0</v>
       </c>
@@ -6221,19 +6225,19 @@
       </c>
       <c r="CB8" t="inlineStr"/>
       <c r="CC8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD8" t="n">
-        <v>4.12</v>
+        <v>2.22</v>
       </c>
       <c r="CE8" t="n">
-        <v>11.09</v>
+        <v>11.46</v>
       </c>
       <c r="CF8" t="n">
-        <v>1248305</v>
+        <v>97892</v>
       </c>
       <c r="CG8" t="n">
-        <v>513.27</v>
+        <v>306.51</v>
       </c>
       <c r="CH8" t="inlineStr">
         <is>
@@ -6242,7 +6246,7 @@
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>Institutional tide in — fii+dii both accumulating; recent filing: general updates [sheets tab 4]; 3/3 fortress layers at vpoc floor</t>
+          <t>Institutional tide in — fii+dii both accumulating; recent filing: no recent filing; 3/3 fortress layers at vpoc floor; post-earnings drift active 🔥</t>
         </is>
       </c>
       <c r="CJ8" t="b">
@@ -6294,7 +6298,7 @@
         <v>56</v>
       </c>
       <c r="CZ8" t="n">
-        <v>535.45</v>
+        <v>329.43</v>
       </c>
       <c r="DA8" t="b">
         <v>0</v>
@@ -6303,23 +6307,23 @@
         <v>0</v>
       </c>
       <c r="DC8" t="n">
-        <v>507.42</v>
+        <v>292.36</v>
       </c>
       <c r="DD8" t="n">
-        <v>507.42</v>
+        <v>292.36</v>
       </c>
       <c r="DE8" t="n">
-        <v>667.25</v>
+        <v>398.46</v>
       </c>
       <c r="DF8" t="n">
-        <v>821.23</v>
+        <v>490.42</v>
       </c>
       <c r="DG8" t="n">
-        <v>1026.54</v>
+        <v>613.02</v>
       </c>
       <c r="DH8" t="inlineStr">
         <is>
-          <t>Sell 30% | Move stop to T1 ₹513.27</t>
+          <t>Sell 30% | Move stop to T1 ₹306.51</t>
         </is>
       </c>
       <c r="DI8" t="inlineStr">
@@ -6333,11 +6337,11 @@
         </is>
       </c>
       <c r="DK8" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="DL8" t="inlineStr">
         <is>
-          <t>🔵 PROBE — SMALL BUY ₹508.14</t>
+          <t>🔵 PROBE — SMALL BUY ₹303.44</t>
         </is>
       </c>
       <c r="DM8" t="inlineStr">
@@ -6349,7 +6353,7 @@
         <v>25</v>
       </c>
       <c r="DO8" t="n">
-        <v>508.1373</v>
+        <v>303.4449</v>
       </c>
       <c r="DP8" t="b">
         <v>0</v>
@@ -6367,21 +6371,21 @@
         <v>1</v>
       </c>
       <c r="DU8" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="DV8" t="n">
-        <v>38175</v>
+        <v>21896</v>
       </c>
       <c r="DW8" t="inlineStr">
         <is>
-          <t>73 sh | ₹38,175 | 25% deploy | Risk ₹1,619</t>
+          <t>71 sh | ₹21,896 | 25% deploy | Risk ₹1,627</t>
         </is>
       </c>
       <c r="DX8" t="n">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="DY8" t="n">
-        <v>22.18</v>
+        <v>22.92</v>
       </c>
       <c r="DZ8" t="inlineStr">
         <is>
@@ -6392,16 +6396,16 @@
         <v>1</v>
       </c>
       <c r="EB8" t="n">
-        <v>18.58</v>
+        <v>18.41</v>
       </c>
       <c r="EC8" t="n">
-        <v>0.01</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MONARCH</t>
+          <t>CONCOR</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -6410,10 +6414,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>308.4</v>
+        <v>522.95</v>
       </c>
       <c r="D9" t="n">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="E9" t="n">
         <v>200</v>
@@ -6429,7 +6433,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I9" t="n">
         <v>30</v>
@@ -6441,40 +6445,40 @@
         <v>15</v>
       </c>
       <c r="L9" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="M9" t="n">
-        <v>306.51</v>
+        <v>513.27</v>
       </c>
       <c r="N9" t="n">
-        <v>325.59</v>
+        <v>539.59</v>
       </c>
       <c r="O9" t="n">
-        <v>292.36</v>
+        <v>507.42</v>
       </c>
       <c r="P9" t="n">
-        <v>398.46</v>
+        <v>667.25</v>
       </c>
       <c r="Q9" t="n">
-        <v>490.42</v>
+        <v>821.23</v>
       </c>
       <c r="R9" t="n">
-        <v>613.02</v>
+        <v>1026.54</v>
       </c>
       <c r="S9" t="n">
-        <v>5.2</v>
+        <v>2.97</v>
       </c>
       <c r="T9" t="n">
-        <v>2.88</v>
+        <v>5.05</v>
       </c>
       <c r="U9" t="n">
-        <v>62.1</v>
+        <v>58.8</v>
       </c>
       <c r="V9" t="n">
-        <v>59.9</v>
+        <v>57.7</v>
       </c>
       <c r="W9" t="n">
-        <v>30</v>
+        <v>46.8</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -6488,7 +6492,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>DISTRIBUTION 🔴</t>
+          <t>NEUTRAL ↔</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -6498,7 +6502,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>₹297.40–₹315.27</t>
+          <t>₹504.56–₹523.85</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -6510,7 +6514,7 @@
         <v>1.4</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.83</v>
+        <v>1.08</v>
       </c>
       <c r="AF9" t="b">
         <v>1</v>
@@ -6525,7 +6529,7 @@
         <v>1</v>
       </c>
       <c r="AJ9" t="n">
-        <v>5.03</v>
+        <v>37.44</v>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
@@ -6552,12 +6556,12 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>No recent filing</t>
+          <t>General updates [SHEETS Tab 4]</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>Results just 1td ago — fresh data</t>
+          <t>Results in 7td — caution</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
@@ -6570,7 +6574,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>52W: 22.7% from ₹399 [23% from 52W high] +0pts</t>
+          <t>52W: 19.8% from ₹652 [20% from 52W high] +0pts</t>
         </is>
       </c>
       <c r="AU9" t="n">
@@ -6578,29 +6582,29 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>ATR-V: -6% compressed [EXPANDING]</t>
+          <t>ATR-V: 9% compressed [🌀 COILING (+4pts)]</t>
         </is>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX9" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>🔴 VDU 3-bar + price drop -1.3% — DISTRIBUTION (-3pts)</t>
+        </is>
+      </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>🔥 HOT PEAD — 4.8% drift 1td post-results (+10pts)</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="BB9" t="inlineStr"/>
       <c r="BC9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -6617,25 +6621,25 @@
         </is>
       </c>
       <c r="BH9" t="n">
-        <v>292.36</v>
+        <v>507.42</v>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>Initial stop ₹292.36</t>
+          <t>Initial stop ₹507.42</t>
         </is>
       </c>
       <c r="BJ9" t="b">
         <v>0</v>
       </c>
       <c r="BK9" t="n">
-        <v>467</v>
+        <v>483</v>
       </c>
       <c r="BL9" t="n">
-        <v>144022.8</v>
+        <v>252584.85</v>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>467 shares · ₹144,023  (risk ₹7,500)</t>
+          <t>483 shares · ₹252,585  (risk ₹7,500)</t>
         </is>
       </c>
       <c r="BN9" t="n">
@@ -6650,23 +6654,19 @@
         </is>
       </c>
       <c r="BQ9" t="n">
-        <v>54.8</v>
+        <v>38.4</v>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 54.8% (t(df=4))</t>
+          <t>⚠️ MC survival 38.4% (t(df=4))</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>DISTRIBUTION</t>
-        </is>
-      </c>
-      <c r="BT9" t="inlineStr">
-        <is>
-          <t>🔴 CVD Diverge — distribution</t>
-        </is>
-      </c>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="BT9" t="inlineStr"/>
       <c r="BU9" t="b">
         <v>0</v>
       </c>
@@ -6688,19 +6688,19 @@
       </c>
       <c r="CB9" t="inlineStr"/>
       <c r="CC9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CD9" t="n">
-        <v>2.22</v>
+        <v>4.12</v>
       </c>
       <c r="CE9" t="n">
-        <v>11.46</v>
+        <v>11.09</v>
       </c>
       <c r="CF9" t="n">
-        <v>97892</v>
+        <v>1248305</v>
       </c>
       <c r="CG9" t="n">
-        <v>306.51</v>
+        <v>513.27</v>
       </c>
       <c r="CH9" t="inlineStr">
         <is>
@@ -6709,7 +6709,7 @@
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>Institutional tide in — fii+dii both accumulating; recent filing: no recent filing; 3/3 fortress layers at vpoc floor; post-earnings drift active 🔥</t>
+          <t>Institutional tide in — fii+dii both accumulating; recent filing: general updates [sheets tab 4]; 3/3 fortress layers at vpoc floor</t>
         </is>
       </c>
       <c r="CJ9" t="b">
@@ -6761,7 +6761,7 @@
         <v>56</v>
       </c>
       <c r="CZ9" t="n">
-        <v>329.43</v>
+        <v>535.45</v>
       </c>
       <c r="DA9" t="b">
         <v>0</v>
@@ -6770,23 +6770,23 @@
         <v>0</v>
       </c>
       <c r="DC9" t="n">
-        <v>292.36</v>
+        <v>507.42</v>
       </c>
       <c r="DD9" t="n">
-        <v>292.36</v>
+        <v>507.42</v>
       </c>
       <c r="DE9" t="n">
-        <v>398.46</v>
+        <v>667.25</v>
       </c>
       <c r="DF9" t="n">
-        <v>490.42</v>
+        <v>821.23</v>
       </c>
       <c r="DG9" t="n">
-        <v>613.02</v>
+        <v>1026.54</v>
       </c>
       <c r="DH9" t="inlineStr">
         <is>
-          <t>Sell 30% | Move stop to T1 ₹306.51</t>
+          <t>Sell 30% | Move stop to T1 ₹513.27</t>
         </is>
       </c>
       <c r="DI9" t="inlineStr">
@@ -6800,11 +6800,11 @@
         </is>
       </c>
       <c r="DK9" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="DL9" t="inlineStr">
         <is>
-          <t>🔵 PROBE — SMALL BUY ₹303.44</t>
+          <t>🔵 PROBE — SMALL BUY ₹508.14</t>
         </is>
       </c>
       <c r="DM9" t="inlineStr">
@@ -6816,7 +6816,7 @@
         <v>25</v>
       </c>
       <c r="DO9" t="n">
-        <v>303.4449</v>
+        <v>508.1373</v>
       </c>
       <c r="DP9" t="b">
         <v>0</v>
@@ -6834,21 +6834,21 @@
         <v>1</v>
       </c>
       <c r="DU9" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="DV9" t="n">
-        <v>21896</v>
+        <v>38175</v>
       </c>
       <c r="DW9" t="inlineStr">
         <is>
-          <t>71 sh | ₹21,896 | 25% deploy | Risk ₹1,627</t>
+          <t>73 sh | ₹38,175 | 25% deploy | Risk ₹1,619</t>
         </is>
       </c>
       <c r="DX9" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="DY9" t="n">
-        <v>22.92</v>
+        <v>22.18</v>
       </c>
       <c r="DZ9" t="inlineStr">
         <is>
@@ -6859,10 +6859,10 @@
         <v>1</v>
       </c>
       <c r="EB9" t="n">
-        <v>18.58</v>
+        <v>18.41</v>
       </c>
       <c r="EC9" t="n">
-        <v>0.01</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="10">
@@ -7113,11 +7113,11 @@
         </is>
       </c>
       <c r="BQ10" t="n">
-        <v>38.8</v>
+        <v>42</v>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 38.8% (t(df=4))</t>
+          <t>⚠️ MC survival 42.0% (t(df=4))</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
@@ -7318,10 +7318,10 @@
         <v>1</v>
       </c>
       <c r="EB10" t="n">
-        <v>18.58</v>
+        <v>18.41</v>
       </c>
       <c r="EC10" t="n">
-        <v>0.01</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="11">
@@ -7572,11 +7572,11 @@
         </is>
       </c>
       <c r="BQ11" t="n">
-        <v>64</v>
+        <v>62.8</v>
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 64.0% (t(df=4))</t>
+          <t>⚠️ MC survival 62.8% (t(df=4))</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
@@ -7783,10 +7783,10 @@
         <v>1</v>
       </c>
       <c r="EB11" t="n">
-        <v>18.58</v>
+        <v>18.41</v>
       </c>
       <c r="EC11" t="n">
-        <v>0.01</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="12">
@@ -8037,11 +8037,11 @@
         </is>
       </c>
       <c r="BQ12" t="n">
-        <v>49.2</v>
+        <v>50.4</v>
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 49.2% (t(df=4))</t>
+          <t>⚠️ MC survival 50.4% (t(df=4))</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
@@ -8244,10 +8244,10 @@
         <v>1</v>
       </c>
       <c r="EB12" t="n">
-        <v>18.58</v>
+        <v>18.41</v>
       </c>
       <c r="EC12" t="n">
-        <v>0.01</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="13">
@@ -8498,11 +8498,11 @@
         </is>
       </c>
       <c r="BQ13" t="n">
-        <v>54.2</v>
+        <v>54.6</v>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 54.2% (t(df=4))</t>
+          <t>⚠️ MC survival 54.6% (t(df=4))</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
@@ -8705,10 +8705,10 @@
         <v>1</v>
       </c>
       <c r="EB13" t="n">
-        <v>18.58</v>
+        <v>18.41</v>
       </c>
       <c r="EC13" t="n">
-        <v>0.01</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="14">
@@ -8959,11 +8959,11 @@
         </is>
       </c>
       <c r="BQ14" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 41.0% (t(df=4))</t>
+          <t>⚠️ MC survival 39.0% (t(df=4))</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
@@ -9170,16 +9170,16 @@
         <v>1</v>
       </c>
       <c r="EB14" t="n">
-        <v>18.58</v>
+        <v>18.41</v>
       </c>
       <c r="EC14" t="n">
-        <v>0.01</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NOCIL</t>
+          <t>ELGIEQUIP</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -9188,10 +9188,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>167.46</v>
+        <v>524.4</v>
       </c>
       <c r="D15" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E15" t="n">
         <v>200</v>
@@ -9207,7 +9207,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="I15" t="n">
         <v>30</v>
@@ -9216,43 +9216,43 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="L15" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M15" t="n">
-        <v>160.38</v>
+        <v>507.08</v>
       </c>
       <c r="N15" t="n">
-        <v>178.25</v>
+        <v>549.03</v>
       </c>
       <c r="O15" t="n">
-        <v>160.27</v>
+        <v>501.41</v>
       </c>
       <c r="P15" t="n">
-        <v>208.49</v>
+        <v>659.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>256.61</v>
+        <v>811.33</v>
       </c>
       <c r="R15" t="n">
-        <v>320.76</v>
+        <v>1014.16</v>
       </c>
       <c r="S15" t="n">
-        <v>4.29</v>
+        <v>4.38</v>
       </c>
       <c r="T15" t="n">
-        <v>3.49</v>
+        <v>3.42</v>
       </c>
       <c r="U15" t="n">
-        <v>45.3</v>
+        <v>54</v>
       </c>
       <c r="V15" t="n">
-        <v>31.9</v>
+        <v>37.2</v>
       </c>
       <c r="W15" t="n">
-        <v>45.9</v>
+        <v>31.8</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -9276,19 +9276,19 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>₹154.87–₹165.43</t>
+          <t>₹494.38–₹520.09</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ATR-1.00× stop</t>
+          <t>ATR-1.40× stop</t>
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.06</v>
+        <v>5.56</v>
       </c>
       <c r="AF15" t="b">
         <v>0</v>
@@ -9303,7 +9303,7 @@
         <v>1</v>
       </c>
       <c r="AJ15" t="n">
-        <v>6.31</v>
+        <v>11.76</v>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
@@ -9330,17 +9330,17 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>Record date [SHEETS Tab 4] | ❌ ROE(proxy) 3.1% [LOW ⚠️] | D/E:0.5 — weak fundamentals</t>
+          <t>Analysts/institutional investor meet/con. call updates [SHEETS Tab 4]</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>No result date found (neutral)</t>
+          <t>Results in 9td — caution</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>ROE(proxy) 3.1% [LOW ⚠️] | D/E:0.5</t>
+          <t>Not checked</t>
         </is>
       </c>
       <c r="AS15" t="b">
@@ -9348,33 +9348,29 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>52W: 20.6% from ₹211 [21% from 52W high] +0pts</t>
+          <t>52W: 13.8% from ₹608 [APPROACHING HIGH] +3pts</t>
         </is>
       </c>
       <c r="AU15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>ATR-V: -4% compressed [EXPANDING]</t>
+          <t>ATR-V: -1% compressed [EXPANDING]</t>
         </is>
       </c>
       <c r="AW15" t="n">
         <v>0</v>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>🌀 VDU 5-bar deep coil (+7pts)</t>
-        </is>
-      </c>
+      <c r="AX15" t="inlineStr"/>
       <c r="AY15" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AZ15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="BB15" t="inlineStr"/>
       <c r="BC15" t="n">
@@ -9395,25 +9391,25 @@
         </is>
       </c>
       <c r="BH15" t="n">
-        <v>160.27</v>
+        <v>501.41</v>
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>Initial stop ₹160.27</t>
+          <t>Initial stop ₹501.41</t>
         </is>
       </c>
       <c r="BJ15" t="b">
         <v>0</v>
       </c>
       <c r="BK15" t="n">
-        <v>1043</v>
+        <v>326</v>
       </c>
       <c r="BL15" t="n">
-        <v>174660.78</v>
+        <v>170954.4</v>
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>1043 shares · ₹174,661  (risk ₹7,500)</t>
+          <t>326 shares · ₹170,954  (risk ₹7,500)</t>
         </is>
       </c>
       <c r="BN15" t="n">
@@ -9428,11 +9424,11 @@
         </is>
       </c>
       <c r="BQ15" t="n">
-        <v>48</v>
+        <v>48.6</v>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 48.0% (t(df=4))</t>
+          <t>⚠️ MC survival 48.6% (t(df=4))</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
@@ -9465,16 +9461,16 @@
         <v>0</v>
       </c>
       <c r="CD15" t="n">
-        <v>-3.67</v>
+        <v>-3.18</v>
       </c>
       <c r="CE15" t="n">
-        <v>7.19</v>
+        <v>16.42</v>
       </c>
       <c r="CF15" t="n">
-        <v>816342</v>
+        <v>339024</v>
       </c>
       <c r="CG15" t="n">
-        <v>160.38</v>
+        <v>507.08</v>
       </c>
       <c r="CH15" t="inlineStr">
         <is>
@@ -9483,17 +9479,13 @@
       </c>
       <c r="CI15" t="inlineStr">
         <is>
-          <t>Institutional tide in — fii+dii both accumulating; recent filing: record date [sheets tab 4] | ❌ roe(proxy) 3.1% [lo</t>
+          <t>Institutional tide in — fii+dii both accumulating; recent filing: analysts/institutional investor meet/con. call upd</t>
         </is>
       </c>
       <c r="CJ15" t="b">
-        <v>1</v>
-      </c>
-      <c r="CK15" t="inlineStr">
-        <is>
-          <t>⚠️ ROUND_TRIP_RISK — close 167 &lt; 90% of 192</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="CK15" t="inlineStr"/>
       <c r="CL15" t="b">
         <v>0</v>
       </c>
@@ -9539,7 +9531,7 @@
         <v>55</v>
       </c>
       <c r="CZ15" t="n">
-        <v>174.76</v>
+        <v>539.92</v>
       </c>
       <c r="DA15" t="b">
         <v>0</v>
@@ -9548,23 +9540,23 @@
         <v>0</v>
       </c>
       <c r="DC15" t="n">
-        <v>160.27</v>
+        <v>501.41</v>
       </c>
       <c r="DD15" t="n">
-        <v>160.27</v>
+        <v>501.41</v>
       </c>
       <c r="DE15" t="n">
-        <v>208.49</v>
+        <v>659.2</v>
       </c>
       <c r="DF15" t="n">
-        <v>256.61</v>
+        <v>811.33</v>
       </c>
       <c r="DG15" t="n">
-        <v>320.76</v>
+        <v>1014.16</v>
       </c>
       <c r="DH15" t="inlineStr">
         <is>
-          <t>Sell 30% | Move stop to T1 ₹160.38</t>
+          <t>Sell 30% | Move stop to T1 ₹507.08</t>
         </is>
       </c>
       <c r="DI15" t="inlineStr">
@@ -9578,11 +9570,11 @@
         </is>
       </c>
       <c r="DK15" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="DL15" t="inlineStr">
         <is>
-          <t>👁️ WATCHING — score 55/100 · +4.4% vs T1</t>
+          <t>👁️ WATCHING — score 55/100 · +3.4% vs T1</t>
         </is>
       </c>
       <c r="DM15" t="inlineStr">
@@ -9624,7 +9616,7 @@
         <v>0</v>
       </c>
       <c r="DY15" t="n">
-        <v>14.38</v>
+        <v>32.84</v>
       </c>
       <c r="DZ15" t="inlineStr">
         <is>
@@ -9635,16 +9627,16 @@
         <v>1</v>
       </c>
       <c r="EB15" t="n">
-        <v>18.58</v>
+        <v>18.41</v>
       </c>
       <c r="EC15" t="n">
-        <v>0.01</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ELGIEQUIP</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -9653,10 +9645,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>524.4</v>
+        <v>454.05</v>
       </c>
       <c r="D16" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E16" t="n">
         <v>200</v>
@@ -9672,7 +9664,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="I16" t="n">
         <v>30</v>
@@ -9684,44 +9676,44 @@
         <v>15</v>
       </c>
       <c r="L16" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M16" t="n">
-        <v>507.08</v>
+        <v>439.96</v>
       </c>
       <c r="N16" t="n">
-        <v>549.03</v>
+        <v>472.74</v>
       </c>
       <c r="O16" t="n">
-        <v>501.41</v>
+        <v>436.61</v>
       </c>
       <c r="P16" t="n">
-        <v>659.2</v>
+        <v>571.95</v>
       </c>
       <c r="Q16" t="n">
-        <v>811.33</v>
+        <v>703.9400000000001</v>
       </c>
       <c r="R16" t="n">
-        <v>1014.16</v>
+        <v>879.92</v>
       </c>
       <c r="S16" t="n">
-        <v>4.38</v>
+        <v>3.84</v>
       </c>
       <c r="T16" t="n">
-        <v>3.42</v>
+        <v>3.91</v>
       </c>
       <c r="U16" t="n">
-        <v>54</v>
+        <v>51.8</v>
       </c>
       <c r="V16" t="n">
-        <v>37.2</v>
+        <v>37.1</v>
       </c>
       <c r="W16" t="n">
-        <v>31.8</v>
+        <v>22.6</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>MOMENTUM</t>
+          <t>TRANSITION</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -9741,7 +9733,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>₹494.38–₹520.09</t>
+          <t>₹430.30–₹450.40</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -9753,7 +9745,7 @@
         <v>1.4</v>
       </c>
       <c r="AE16" t="n">
-        <v>5.56</v>
+        <v>10.61</v>
       </c>
       <c r="AF16" t="b">
         <v>0</v>
@@ -9768,7 +9760,7 @@
         <v>1</v>
       </c>
       <c r="AJ16" t="n">
-        <v>11.76</v>
+        <v>526.74</v>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
@@ -9795,12 +9787,12 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>Analysts/institutional investor meet/con. call updates [SHEETS Tab 4]</t>
+          <t>Updates [SHEETS Tab 4]</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>Results in 9td — caution</t>
+          <t>No result date found (neutral)</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
@@ -9813,15 +9805,15 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>52W: 13.8% from ₹608 [APPROACHING HIGH] +3pts</t>
+          <t>52W: 7.6% from ₹491 [NEAR 52W HIGH] +5pts</t>
         </is>
       </c>
       <c r="AU16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>ATR-V: -1% compressed [EXPANDING]</t>
+          <t>ATR-V: -11% compressed [EXPANDING]</t>
         </is>
       </c>
       <c r="AW16" t="n">
@@ -9835,7 +9827,7 @@
         <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BB16" t="inlineStr"/>
       <c r="BC16" t="n">
@@ -9856,25 +9848,25 @@
         </is>
       </c>
       <c r="BH16" t="n">
-        <v>501.41</v>
+        <v>436.61</v>
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>Initial stop ₹501.41</t>
+          <t>Initial stop ₹436.61</t>
         </is>
       </c>
       <c r="BJ16" t="b">
         <v>0</v>
       </c>
       <c r="BK16" t="n">
-        <v>326</v>
+        <v>429</v>
       </c>
       <c r="BL16" t="n">
-        <v>170954.4</v>
+        <v>194787.45</v>
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>326 shares · ₹170,954  (risk ₹7,500)</t>
+          <t>429 shares · ₹194,787  (risk ₹7,500)</t>
         </is>
       </c>
       <c r="BN16" t="n">
@@ -9889,11 +9881,11 @@
         </is>
       </c>
       <c r="BQ16" t="n">
-        <v>47.4</v>
+        <v>61.6</v>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 47.4% (t(df=4))</t>
+          <t>⚠️ MC survival 61.6% (t(df=4))</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
@@ -9926,16 +9918,16 @@
         <v>0</v>
       </c>
       <c r="CD16" t="n">
-        <v>-3.18</v>
+        <v>4.92</v>
       </c>
       <c r="CE16" t="n">
-        <v>16.42</v>
+        <v>12.46</v>
       </c>
       <c r="CF16" t="n">
-        <v>339024</v>
+        <v>11239659</v>
       </c>
       <c r="CG16" t="n">
-        <v>507.08</v>
+        <v>439.96</v>
       </c>
       <c r="CH16" t="inlineStr">
         <is>
@@ -9944,7 +9936,7 @@
       </c>
       <c r="CI16" t="inlineStr">
         <is>
-          <t>Institutional tide in — fii+dii both accumulating; recent filing: analysts/institutional investor meet/con. call upd</t>
+          <t>Institutional tide in — fii+dii both accumulating; recent filing: updates [sheets tab 4]</t>
         </is>
       </c>
       <c r="CJ16" t="b">
@@ -9979,24 +9971,24 @@
         <v>0</v>
       </c>
       <c r="CU16" t="n">
-        <v>0.132</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="CV16" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="CW16" t="n">
         <v>-5</v>
       </c>
       <c r="CX16" t="inlineStr">
         <is>
-          <t>🧠 Sniper Bayes 13% — LOW</t>
+          <t>🧠 Sniper Bayes 7% — LOW</t>
         </is>
       </c>
       <c r="CY16" t="n">
         <v>55</v>
       </c>
       <c r="CZ16" t="n">
-        <v>539.92</v>
+        <v>464.88</v>
       </c>
       <c r="DA16" t="b">
         <v>0</v>
@@ -10005,23 +9997,23 @@
         <v>0</v>
       </c>
       <c r="DC16" t="n">
-        <v>501.41</v>
+        <v>436.61</v>
       </c>
       <c r="DD16" t="n">
-        <v>501.41</v>
+        <v>436.61</v>
       </c>
       <c r="DE16" t="n">
-        <v>659.2</v>
+        <v>571.95</v>
       </c>
       <c r="DF16" t="n">
-        <v>811.33</v>
+        <v>703.9400000000001</v>
       </c>
       <c r="DG16" t="n">
-        <v>1014.16</v>
+        <v>879.92</v>
       </c>
       <c r="DH16" t="inlineStr">
         <is>
-          <t>Sell 30% | Move stop to T1 ₹507.08</t>
+          <t>Sell 30% | Move stop to T1 ₹439.96</t>
         </is>
       </c>
       <c r="DI16" t="inlineStr">
@@ -10035,11 +10027,11 @@
         </is>
       </c>
       <c r="DK16" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="DL16" t="inlineStr">
         <is>
-          <t>👁️ WATCHING — score 55/100 · +3.4% vs T1</t>
+          <t>👁️ WATCHING — score 55/100 · +3.2% vs T1</t>
         </is>
       </c>
       <c r="DM16" t="inlineStr">
@@ -10081,7 +10073,7 @@
         <v>0</v>
       </c>
       <c r="DY16" t="n">
-        <v>32.84</v>
+        <v>24.92</v>
       </c>
       <c r="DZ16" t="inlineStr">
         <is>
@@ -10092,16 +10084,16 @@
         <v>1</v>
       </c>
       <c r="EB16" t="n">
-        <v>18.58</v>
+        <v>18.41</v>
       </c>
       <c r="EC16" t="n">
-        <v>0.01</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>PRICOLLTD</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -10110,7 +10102,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>454.05</v>
+        <v>571.95</v>
       </c>
       <c r="D17" t="n">
         <v>100</v>
@@ -10138,43 +10130,43 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="L17" t="n">
         <v>20</v>
       </c>
       <c r="M17" t="n">
-        <v>439.96</v>
+        <v>606.88</v>
       </c>
       <c r="N17" t="n">
-        <v>472.74</v>
+        <v>603.29</v>
       </c>
       <c r="O17" t="n">
-        <v>436.61</v>
+        <v>542.7</v>
       </c>
       <c r="P17" t="n">
-        <v>571.95</v>
+        <v>788.9400000000001</v>
       </c>
       <c r="Q17" t="n">
-        <v>703.9400000000001</v>
+        <v>971.01</v>
       </c>
       <c r="R17" t="n">
-        <v>879.92</v>
+        <v>1213.76</v>
       </c>
       <c r="S17" t="n">
-        <v>3.84</v>
+        <v>5.11</v>
       </c>
       <c r="T17" t="n">
-        <v>3.91</v>
+        <v>2.93</v>
       </c>
       <c r="U17" t="n">
-        <v>51.8</v>
+        <v>53.6</v>
       </c>
       <c r="V17" t="n">
-        <v>37.1</v>
+        <v>36.6</v>
       </c>
       <c r="W17" t="n">
-        <v>22.6</v>
+        <v>22.2</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -10193,12 +10185,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>ABOVE</t>
+          <t>BELOW</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>₹430.30–₹450.40</t>
+          <t>₹589.14–₹624.03</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -10210,13 +10202,13 @@
         <v>1.4</v>
       </c>
       <c r="AE17" t="n">
-        <v>10.61</v>
+        <v>2.38</v>
       </c>
       <c r="AF17" t="b">
         <v>0</v>
       </c>
       <c r="AG17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH17" t="b">
         <v>1</v>
@@ -10225,7 +10217,7 @@
         <v>1</v>
       </c>
       <c r="AJ17" t="n">
-        <v>526.74</v>
+        <v>18.54</v>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
@@ -10252,7 +10244,7 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>Updates [SHEETS Tab 4]</t>
+          <t>Record date [SHEETS Tab 4] | ⚠️ ROE(proxy) unverifiable — filing capped</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
@@ -10262,7 +10254,7 @@
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>Not checked</t>
+          <t>ROE quality data unavailable</t>
         </is>
       </c>
       <c r="AS17" t="b">
@@ -10270,15 +10262,15 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>52W: 7.6% from ₹491 [NEAR 52W HIGH] +5pts</t>
+          <t>52W: 17.6% from ₹694 [18% from 52W high] +0pts</t>
         </is>
       </c>
       <c r="AU17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>ATR-V: -11% compressed [EXPANDING]</t>
+          <t>ATR-V: -10% compressed [EXPANDING]</t>
         </is>
       </c>
       <c r="AW17" t="n">
@@ -10292,7 +10284,7 @@
         <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BB17" t="inlineStr"/>
       <c r="BC17" t="n">
@@ -10313,25 +10305,25 @@
         </is>
       </c>
       <c r="BH17" t="n">
-        <v>436.61</v>
+        <v>542.7</v>
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>Initial stop ₹436.61</t>
+          <t>Initial stop ₹542.70</t>
         </is>
       </c>
       <c r="BJ17" t="b">
         <v>0</v>
       </c>
       <c r="BK17" t="n">
-        <v>429</v>
+        <v>256</v>
       </c>
       <c r="BL17" t="n">
-        <v>194787.45</v>
+        <v>146419.2</v>
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>429 shares · ₹194,787  (risk ₹7,500)</t>
+          <t>256 shares · ₹146,419  (risk ₹7,500)</t>
         </is>
       </c>
       <c r="BN17" t="n">
@@ -10346,19 +10338,23 @@
         </is>
       </c>
       <c r="BQ17" t="n">
-        <v>64.40000000000001</v>
+        <v>60.2</v>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 64.4% (t(df=4))</t>
+          <t>⚠️ MC survival 60.2% (t(df=4))</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="BT17" t="inlineStr"/>
+          <t>ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="BT17" t="inlineStr">
+        <is>
+          <t>🟢 CVD Accum — smart money</t>
+        </is>
+      </c>
       <c r="BU17" t="b">
         <v>0</v>
       </c>
@@ -10383,16 +10379,16 @@
         <v>0</v>
       </c>
       <c r="CD17" t="n">
-        <v>4.92</v>
+        <v>-1.46</v>
       </c>
       <c r="CE17" t="n">
-        <v>12.46</v>
+        <v>20.89</v>
       </c>
       <c r="CF17" t="n">
-        <v>11239659</v>
+        <v>287537</v>
       </c>
       <c r="CG17" t="n">
-        <v>439.96</v>
+        <v>606.88</v>
       </c>
       <c r="CH17" t="inlineStr">
         <is>
@@ -10401,7 +10397,7 @@
       </c>
       <c r="CI17" t="inlineStr">
         <is>
-          <t>Institutional tide in — fii+dii both accumulating; recent filing: updates [sheets tab 4]</t>
+          <t>Institutional tide in — fii+dii both accumulating; recent filing: record date [sheets tab 4] | ⚠️ roe(proxy) unverif; 2/3 fortress layers at vpoc floor</t>
         </is>
       </c>
       <c r="CJ17" t="b">
@@ -10436,24 +10432,24 @@
         <v>0</v>
       </c>
       <c r="CU17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.136</v>
       </c>
       <c r="CV17" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="CW17" t="n">
         <v>-5</v>
       </c>
       <c r="CX17" t="inlineStr">
         <is>
-          <t>🧠 Sniper Bayes 7% — LOW</t>
+          <t>🧠 Sniper Bayes 14% — LOW</t>
         </is>
       </c>
       <c r="CY17" t="n">
         <v>55</v>
       </c>
       <c r="CZ17" t="n">
-        <v>464.88</v>
+        <v>648.66</v>
       </c>
       <c r="DA17" t="b">
         <v>0</v>
@@ -10462,23 +10458,23 @@
         <v>0</v>
       </c>
       <c r="DC17" t="n">
-        <v>436.61</v>
+        <v>542.7</v>
       </c>
       <c r="DD17" t="n">
-        <v>436.61</v>
+        <v>542.7</v>
       </c>
       <c r="DE17" t="n">
-        <v>571.95</v>
+        <v>788.9400000000001</v>
       </c>
       <c r="DF17" t="n">
-        <v>703.9400000000001</v>
+        <v>971.01</v>
       </c>
       <c r="DG17" t="n">
-        <v>879.92</v>
+        <v>1213.76</v>
       </c>
       <c r="DH17" t="inlineStr">
         <is>
-          <t>Sell 30% | Move stop to T1 ₹439.96</t>
+          <t>Sell 30% | Move stop to T1 ₹606.88</t>
         </is>
       </c>
       <c r="DI17" t="inlineStr">
@@ -10492,11 +10488,11 @@
         </is>
       </c>
       <c r="DK17" t="n">
-        <v>3.2</v>
+        <v>-5.8</v>
       </c>
       <c r="DL17" t="inlineStr">
         <is>
-          <t>👁️ WATCHING — score 55/100 · +3.2% vs T1</t>
+          <t>👁️ WATCHING — score 55/100 · -5.8% vs T1</t>
         </is>
       </c>
       <c r="DM17" t="inlineStr">
@@ -10538,7 +10534,7 @@
         <v>0</v>
       </c>
       <c r="DY17" t="n">
-        <v>24.92</v>
+        <v>41.78</v>
       </c>
       <c r="DZ17" t="inlineStr">
         <is>
@@ -10549,16 +10545,16 @@
         <v>1</v>
       </c>
       <c r="EB17" t="n">
-        <v>18.58</v>
+        <v>18.41</v>
       </c>
       <c r="EC17" t="n">
-        <v>0.01</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>PRICOLLTD</t>
+          <t>NOCIL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -10567,26 +10563,26 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>571.95</v>
+        <v>167.46</v>
       </c>
       <c r="D18" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="E18" t="n">
         <v>200</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>🟡 HIGH</t>
+          <t>🟠 MODERATE</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>HALF 50%</t>
+          <t>QTR 25%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I18" t="n">
         <v>30</v>
@@ -10595,47 +10591,47 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L18" t="n">
         <v>20</v>
       </c>
       <c r="M18" t="n">
-        <v>606.88</v>
+        <v>160.38</v>
       </c>
       <c r="N18" t="n">
-        <v>603.29</v>
+        <v>178.25</v>
       </c>
       <c r="O18" t="n">
-        <v>542.7</v>
+        <v>160.27</v>
       </c>
       <c r="P18" t="n">
-        <v>788.9400000000001</v>
+        <v>208.49</v>
       </c>
       <c r="Q18" t="n">
-        <v>971.01</v>
+        <v>256.61</v>
       </c>
       <c r="R18" t="n">
-        <v>1213.76</v>
+        <v>320.76</v>
       </c>
       <c r="S18" t="n">
-        <v>5.11</v>
+        <v>4.29</v>
       </c>
       <c r="T18" t="n">
-        <v>2.93</v>
+        <v>3.49</v>
       </c>
       <c r="U18" t="n">
-        <v>53.6</v>
+        <v>45.3</v>
       </c>
       <c r="V18" t="n">
-        <v>36.6</v>
+        <v>31.9</v>
       </c>
       <c r="W18" t="n">
-        <v>22.2</v>
+        <v>45.9</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>TRANSITION</t>
+          <t>MOMENTUM</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -10650,30 +10646,30 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>BELOW</t>
+          <t>ABOVE</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>₹589.14–₹624.03</t>
+          <t>₹154.87–₹165.43</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ATR-1.40× stop</t>
+          <t>ATR-1.00× stop</t>
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.38</v>
+        <v>1.06</v>
       </c>
       <c r="AF18" t="b">
         <v>0</v>
       </c>
       <c r="AG18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="b">
         <v>1</v>
@@ -10682,7 +10678,7 @@
         <v>1</v>
       </c>
       <c r="AJ18" t="n">
-        <v>18.54</v>
+        <v>6.31</v>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
@@ -10709,7 +10705,7 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>Record date [SHEETS Tab 4] | ⚠️ ROE(proxy) unverifiable — filing capped</t>
+          <t>Record date [SHEETS Tab 4] | ❌ ROE(proxy) 3.1% [LOW ⚠️] | D/E:0.5 — weak fundamentals</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
@@ -10719,7 +10715,7 @@
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>ROE quality data unavailable</t>
+          <t>ROE(proxy) 3.1% [LOW ⚠️] | D/E:0.5</t>
         </is>
       </c>
       <c r="AS18" t="b">
@@ -10727,7 +10723,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>52W: 17.6% from ₹694 [18% from 52W high] +0pts</t>
+          <t>52W: 20.6% from ₹211 [21% from 52W high] +0pts</t>
         </is>
       </c>
       <c r="AU18" t="n">
@@ -10735,21 +10731,25 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>ATR-V: -10% compressed [EXPANDING]</t>
+          <t>ATR-V: -4% compressed [EXPANDING]</t>
         </is>
       </c>
       <c r="AW18" t="n">
         <v>0</v>
       </c>
-      <c r="AX18" t="inlineStr"/>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>🔴 VDU 5-bar + price drop -11.3% — DISTRIBUTION (-3pts)</t>
+        </is>
+      </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="BB18" t="inlineStr"/>
       <c r="BC18" t="n">
@@ -10770,25 +10770,25 @@
         </is>
       </c>
       <c r="BH18" t="n">
-        <v>542.7</v>
+        <v>160.27</v>
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>Initial stop ₹542.70</t>
+          <t>Initial stop ₹160.27</t>
         </is>
       </c>
       <c r="BJ18" t="b">
         <v>0</v>
       </c>
       <c r="BK18" t="n">
-        <v>256</v>
+        <v>1043</v>
       </c>
       <c r="BL18" t="n">
-        <v>146419.2</v>
+        <v>174660.78</v>
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>256 shares · ₹146,419  (risk ₹7,500)</t>
+          <t>1043 shares · ₹174,661  (risk ₹7,500)</t>
         </is>
       </c>
       <c r="BN18" t="n">
@@ -10803,23 +10803,19 @@
         </is>
       </c>
       <c r="BQ18" t="n">
-        <v>60.4</v>
+        <v>47</v>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 60.4% (t(df=4))</t>
+          <t>⚠️ MC survival 47.0% (t(df=4))</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>ACCUMULATION</t>
-        </is>
-      </c>
-      <c r="BT18" t="inlineStr">
-        <is>
-          <t>🟢 CVD Accum — smart money</t>
-        </is>
-      </c>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="BT18" t="inlineStr"/>
       <c r="BU18" t="b">
         <v>0</v>
       </c>
@@ -10844,16 +10840,16 @@
         <v>0</v>
       </c>
       <c r="CD18" t="n">
-        <v>-1.46</v>
+        <v>-3.67</v>
       </c>
       <c r="CE18" t="n">
-        <v>20.89</v>
+        <v>7.19</v>
       </c>
       <c r="CF18" t="n">
-        <v>287537</v>
+        <v>816342</v>
       </c>
       <c r="CG18" t="n">
-        <v>606.88</v>
+        <v>160.38</v>
       </c>
       <c r="CH18" t="inlineStr">
         <is>
@@ -10862,13 +10858,17 @@
       </c>
       <c r="CI18" t="inlineStr">
         <is>
-          <t>Institutional tide in — fii+dii both accumulating; recent filing: record date [sheets tab 4] | ⚠️ roe(proxy) unverif; 2/3 fortress layers at vpoc floor</t>
+          <t>Institutional tide in — fii+dii both accumulating; recent filing: record date [sheets tab 4] | ❌ roe(proxy) 3.1% [lo</t>
         </is>
       </c>
       <c r="CJ18" t="b">
-        <v>0</v>
-      </c>
-      <c r="CK18" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="CK18" t="inlineStr">
+        <is>
+          <t>⚠️ ROUND_TRIP_RISK — close 167 &lt; 90% of 192</t>
+        </is>
+      </c>
       <c r="CL18" t="b">
         <v>0</v>
       </c>
@@ -10897,24 +10897,24 @@
         <v>0</v>
       </c>
       <c r="CU18" t="n">
-        <v>0.136</v>
+        <v>0.132</v>
       </c>
       <c r="CV18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="CW18" t="n">
         <v>-5</v>
       </c>
       <c r="CX18" t="inlineStr">
         <is>
-          <t>🧠 Sniper Bayes 14% — LOW</t>
+          <t>🧠 Sniper Bayes 13% — LOW</t>
         </is>
       </c>
       <c r="CY18" t="n">
         <v>55</v>
       </c>
       <c r="CZ18" t="n">
-        <v>648.66</v>
+        <v>174.76</v>
       </c>
       <c r="DA18" t="b">
         <v>0</v>
@@ -10923,23 +10923,23 @@
         <v>0</v>
       </c>
       <c r="DC18" t="n">
-        <v>542.7</v>
+        <v>160.27</v>
       </c>
       <c r="DD18" t="n">
-        <v>542.7</v>
+        <v>160.27</v>
       </c>
       <c r="DE18" t="n">
-        <v>788.9400000000001</v>
+        <v>208.49</v>
       </c>
       <c r="DF18" t="n">
-        <v>971.01</v>
+        <v>256.61</v>
       </c>
       <c r="DG18" t="n">
-        <v>1213.76</v>
+        <v>320.76</v>
       </c>
       <c r="DH18" t="inlineStr">
         <is>
-          <t>Sell 30% | Move stop to T1 ₹606.88</t>
+          <t>Sell 30% | Move stop to T1 ₹160.38</t>
         </is>
       </c>
       <c r="DI18" t="inlineStr">
@@ -10953,11 +10953,11 @@
         </is>
       </c>
       <c r="DK18" t="n">
-        <v>-5.8</v>
+        <v>4.4</v>
       </c>
       <c r="DL18" t="inlineStr">
         <is>
-          <t>👁️ WATCHING — score 55/100 · -5.8% vs T1</t>
+          <t>👁️ WATCHING — score 55/100 · +4.4% vs T1</t>
         </is>
       </c>
       <c r="DM18" t="inlineStr">
@@ -10999,7 +10999,7 @@
         <v>0</v>
       </c>
       <c r="DY18" t="n">
-        <v>41.78</v>
+        <v>14.38</v>
       </c>
       <c r="DZ18" t="inlineStr">
         <is>
@@ -11010,10 +11010,10 @@
         <v>1</v>
       </c>
       <c r="EB18" t="n">
-        <v>18.58</v>
+        <v>18.41</v>
       </c>
       <c r="EC18" t="n">
-        <v>0.01</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="19">
@@ -11264,11 +11264,11 @@
         </is>
       </c>
       <c r="BQ19" t="n">
-        <v>41.6</v>
+        <v>43</v>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 41.6% (t(df=4))</t>
+          <t>⚠️ MC survival 43.0% (t(df=4))</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
@@ -11467,10 +11467,10 @@
         <v>1</v>
       </c>
       <c r="EB19" t="n">
-        <v>18.58</v>
+        <v>18.41</v>
       </c>
       <c r="EC19" t="n">
-        <v>0.01</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="20">
@@ -11721,11 +11721,11 @@
         </is>
       </c>
       <c r="BQ20" t="n">
-        <v>48.8</v>
+        <v>45</v>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 48.8% (t(df=4))</t>
+          <t>⚠️ MC survival 45.0% (t(df=4))</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
@@ -11924,10 +11924,10 @@
         <v>1</v>
       </c>
       <c r="EB20" t="n">
-        <v>18.58</v>
+        <v>18.41</v>
       </c>
       <c r="EC20" t="n">
-        <v>0.01</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="21">
@@ -11945,7 +11945,7 @@
         <v>559.5</v>
       </c>
       <c r="D21" t="n">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="E21" t="n">
         <v>200</v>
@@ -11961,7 +11961,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="I21" t="n">
         <v>30</v>
@@ -12118,17 +12118,17 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>🌀 VDU 4-bar confirmed (+5pts)</t>
+          <t>🔴 VDU 4-bar + price drop -4.2% — DISTRIBUTION (-3pts)</t>
         </is>
       </c>
       <c r="AY21" t="n">
-        <v>5</v>
+        <v>-3</v>
       </c>
       <c r="AZ21" t="n">
         <v>4</v>
       </c>
       <c r="BA21" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="BB21" t="inlineStr"/>
       <c r="BC21" t="n">
@@ -12182,11 +12182,11 @@
         </is>
       </c>
       <c r="BQ21" t="n">
-        <v>50.6</v>
+        <v>45.4</v>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 50.6% (t(df=4))</t>
+          <t>⚠️ MC survival 45.4% (t(df=4))</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
@@ -12385,10 +12385,10 @@
         <v>1</v>
       </c>
       <c r="EB21" t="n">
-        <v>18.58</v>
+        <v>18.41</v>
       </c>
       <c r="EC21" t="n">
-        <v>0.01</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="22">
@@ -12639,11 +12639,11 @@
         </is>
       </c>
       <c r="BQ22" t="n">
-        <v>60.2</v>
+        <v>66.2</v>
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 60.2% (t(df=4))</t>
+          <t>⚠️ MC survival 66.2% (t(df=4)) ⚠️ HIGH VARIANCE (71.2% vs 61.2% — use caution)</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
@@ -12852,10 +12852,10 @@
         <v>1</v>
       </c>
       <c r="EB22" t="n">
-        <v>18.58</v>
+        <v>18.41</v>
       </c>
       <c r="EC22" t="n">
-        <v>0.01</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="23">
@@ -13106,11 +13106,11 @@
         </is>
       </c>
       <c r="BQ23" t="n">
-        <v>26</v>
+        <v>26.2</v>
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 26.0% (t(df=4))</t>
+          <t>⚠️ MC survival 26.2% (t(df=4)) ⚠️ HIGH VARIANCE (22.0% vs 30.4% — use caution)</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
@@ -13311,10 +13311,10 @@
         <v>1</v>
       </c>
       <c r="EB23" t="n">
-        <v>18.58</v>
+        <v>18.41</v>
       </c>
       <c r="EC23" t="n">
-        <v>0.01</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="24">
@@ -13565,11 +13565,11 @@
         </is>
       </c>
       <c r="BQ24" t="n">
-        <v>59.4</v>
+        <v>56.8</v>
       </c>
       <c r="BR24" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 59.4% (t(df=4))</t>
+          <t>⚠️ MC survival 56.8% (t(df=4))</t>
         </is>
       </c>
       <c r="BS24" t="inlineStr">
@@ -13768,10 +13768,10 @@
         <v>1</v>
       </c>
       <c r="EB24" t="n">
-        <v>18.58</v>
+        <v>18.41</v>
       </c>
       <c r="EC24" t="n">
-        <v>0.01</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="25">
@@ -13789,7 +13789,7 @@
         <v>105.38</v>
       </c>
       <c r="D25" t="n">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="E25" t="n">
         <v>200</v>
@@ -13805,7 +13805,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="I25" t="n">
         <v>30</v>
@@ -13962,17 +13962,17 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>🌀 VDU 3-bar mild (+3pts)</t>
+          <t>🔴 VDU 3-bar + price drop -4.8% — DISTRIBUTION (-3pts)</t>
         </is>
       </c>
       <c r="AY25" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="AZ25" t="n">
         <v>3</v>
       </c>
       <c r="BA25" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="BB25" t="inlineStr"/>
       <c r="BC25" t="n">
@@ -14026,11 +14026,11 @@
         </is>
       </c>
       <c r="BQ25" t="n">
-        <v>33</v>
+        <v>33.4</v>
       </c>
       <c r="BR25" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 33.0% (t(df=4))</t>
+          <t>⚠️ MC survival 33.4% (t(df=4))</t>
         </is>
       </c>
       <c r="BS25" t="inlineStr">
@@ -14237,10 +14237,10 @@
         <v>1</v>
       </c>
       <c r="EB25" t="n">
-        <v>18.58</v>
+        <v>18.41</v>
       </c>
       <c r="EC25" t="n">
-        <v>0.01</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="26">
@@ -14702,10 +14702,10 @@
         <v>1</v>
       </c>
       <c r="EB26" t="n">
-        <v>18.58</v>
+        <v>18.41</v>
       </c>
       <c r="EC26" t="n">
-        <v>0.01</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="27">
@@ -14956,11 +14956,11 @@
         </is>
       </c>
       <c r="BQ27" t="n">
-        <v>45.6</v>
+        <v>41.8</v>
       </c>
       <c r="BR27" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 45.6% (t(df=4))</t>
+          <t>⚠️ MC survival 41.8% (t(df=4))</t>
         </is>
       </c>
       <c r="BS27" t="inlineStr">
@@ -15163,10 +15163,10 @@
         <v>1</v>
       </c>
       <c r="EB27" t="n">
-        <v>18.58</v>
+        <v>18.41</v>
       </c>
       <c r="EC27" t="n">
-        <v>0.01</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="28">
@@ -15417,11 +15417,11 @@
         </is>
       </c>
       <c r="BQ28" t="n">
-        <v>33</v>
+        <v>32.8</v>
       </c>
       <c r="BR28" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 33.0% (t(df=4))</t>
+          <t>⚠️ MC survival 32.8% (t(df=4))</t>
         </is>
       </c>
       <c r="BS28" t="inlineStr">
@@ -15620,10 +15620,10 @@
         <v>1</v>
       </c>
       <c r="EB28" t="n">
-        <v>18.58</v>
+        <v>18.41</v>
       </c>
       <c r="EC28" t="n">
-        <v>0.01</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="29">
@@ -15874,11 +15874,11 @@
         </is>
       </c>
       <c r="BQ29" t="n">
-        <v>52.6</v>
+        <v>49.6</v>
       </c>
       <c r="BR29" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 52.6% (t(df=4))</t>
+          <t>⚠️ MC survival 49.6% (t(df=4)) ⚠️ HIGH VARIANCE (54.0% vs 45.2% — use caution)</t>
         </is>
       </c>
       <c r="BS29" t="inlineStr">
@@ -16077,10 +16077,10 @@
         <v>1</v>
       </c>
       <c r="EB29" t="n">
-        <v>18.58</v>
+        <v>18.41</v>
       </c>
       <c r="EC29" t="n">
-        <v>0.01</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="30">
@@ -16331,11 +16331,11 @@
         </is>
       </c>
       <c r="BQ30" t="n">
-        <v>33.8</v>
+        <v>34.8</v>
       </c>
       <c r="BR30" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 33.8% (t(df=4))</t>
+          <t>⚠️ MC survival 34.8% (t(df=4))</t>
         </is>
       </c>
       <c r="BS30" t="inlineStr">
@@ -16534,10 +16534,10 @@
         <v>1</v>
       </c>
       <c r="EB30" t="n">
-        <v>18.58</v>
+        <v>18.41</v>
       </c>
       <c r="EC30" t="n">
-        <v>0.01</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="31">
@@ -16788,11 +16788,11 @@
         </is>
       </c>
       <c r="BQ31" t="n">
-        <v>54.8</v>
+        <v>48.4</v>
       </c>
       <c r="BR31" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 54.8% (t(df=4))</t>
+          <t>⚠️ MC survival 48.4% (t(df=4))</t>
         </is>
       </c>
       <c r="BS31" t="inlineStr">
@@ -16991,10 +16991,10 @@
         <v>1</v>
       </c>
       <c r="EB31" t="n">
-        <v>18.58</v>
+        <v>18.41</v>
       </c>
       <c r="EC31" t="n">
-        <v>0.01</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="32">
@@ -17249,11 +17249,11 @@
         </is>
       </c>
       <c r="BQ32" t="n">
-        <v>51.8</v>
+        <v>55.6</v>
       </c>
       <c r="BR32" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 51.8% (t(df=4))</t>
+          <t>⚠️ MC survival 55.6% (t(df=4))</t>
         </is>
       </c>
       <c r="BS32" t="inlineStr">
@@ -17452,10 +17452,10 @@
         <v>1</v>
       </c>
       <c r="EB32" t="n">
-        <v>18.58</v>
+        <v>18.41</v>
       </c>
       <c r="EC32" t="n">
-        <v>0.01</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="33">
@@ -17706,11 +17706,11 @@
         </is>
       </c>
       <c r="BQ33" t="n">
-        <v>60.2</v>
+        <v>59.6</v>
       </c>
       <c r="BR33" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 60.2% (t(df=4))</t>
+          <t>⚠️ MC survival 59.6% (t(df=4))</t>
         </is>
       </c>
       <c r="BS33" t="inlineStr">
@@ -17909,10 +17909,10 @@
         <v>1</v>
       </c>
       <c r="EB33" t="n">
-        <v>18.58</v>
+        <v>18.41</v>
       </c>
       <c r="EC33" t="n">
-        <v>0.01</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="34">
@@ -18167,11 +18167,11 @@
         </is>
       </c>
       <c r="BQ34" t="n">
-        <v>30.6</v>
+        <v>29.4</v>
       </c>
       <c r="BR34" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 30.6% (t(df=4))</t>
+          <t>⚠️ MC survival 29.4% (t(df=4))</t>
         </is>
       </c>
       <c r="BS34" t="inlineStr">
@@ -18370,10 +18370,10 @@
         <v>1</v>
       </c>
       <c r="EB34" t="n">
-        <v>18.58</v>
+        <v>18.41</v>
       </c>
       <c r="EC34" t="n">
-        <v>0.01</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="35">
@@ -18391,7 +18391,7 @@
         <v>126.11</v>
       </c>
       <c r="D35" t="n">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="E35" t="n">
         <v>200</v>
@@ -18407,7 +18407,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="I35" t="n">
         <v>30</v>
@@ -18564,17 +18564,17 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>🌀 VDU 3-bar mild (+3pts)</t>
+          <t>🔴 VDU 3-bar + price drop -3.2% — DISTRIBUTION (-3pts)</t>
         </is>
       </c>
       <c r="AY35" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="AZ35" t="n">
         <v>3</v>
       </c>
       <c r="BA35" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="BB35" t="inlineStr"/>
       <c r="BC35" t="n">
@@ -18628,11 +18628,11 @@
         </is>
       </c>
       <c r="BQ35" t="n">
-        <v>46.2</v>
+        <v>41.6</v>
       </c>
       <c r="BR35" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 46.2% (t(df=4))</t>
+          <t>⚠️ MC survival 41.6% (t(df=4))</t>
         </is>
       </c>
       <c r="BS35" t="inlineStr">
@@ -18831,10 +18831,10 @@
         <v>1</v>
       </c>
       <c r="EB35" t="n">
-        <v>18.58</v>
+        <v>18.41</v>
       </c>
       <c r="EC35" t="n">
-        <v>0.01</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="36">
@@ -19085,11 +19085,11 @@
         </is>
       </c>
       <c r="BQ36" t="n">
-        <v>45.8</v>
+        <v>41.8</v>
       </c>
       <c r="BR36" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 45.8% (t(df=4))</t>
+          <t>⚠️ MC survival 41.8% (t(df=4))</t>
         </is>
       </c>
       <c r="BS36" t="inlineStr">
@@ -19292,10 +19292,10 @@
         <v>1</v>
       </c>
       <c r="EB36" t="n">
-        <v>18.58</v>
+        <v>18.41</v>
       </c>
       <c r="EC36" t="n">
-        <v>0.01</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="37">
@@ -19546,11 +19546,11 @@
         </is>
       </c>
       <c r="BQ37" t="n">
-        <v>35.2</v>
+        <v>33.6</v>
       </c>
       <c r="BR37" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 35.2% (t(df=4))</t>
+          <t>⚠️ MC survival 33.6% (t(df=4))</t>
         </is>
       </c>
       <c r="BS37" t="inlineStr">
@@ -19749,10 +19749,10 @@
         <v>1</v>
       </c>
       <c r="EB37" t="n">
-        <v>18.58</v>
+        <v>18.41</v>
       </c>
       <c r="EC37" t="n">
-        <v>0.01</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="38">
@@ -19770,7 +19770,7 @@
         <v>156.95</v>
       </c>
       <c r="D38" t="n">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="E38" t="n">
         <v>200</v>
@@ -19786,7 +19786,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="I38" t="n">
         <v>30</v>
@@ -19943,17 +19943,17 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>🌀 VDU 4-bar confirmed (+5pts)</t>
+          <t>🔴 VDU 4-bar + price drop -3.7% — DISTRIBUTION (-3pts)</t>
         </is>
       </c>
       <c r="AY38" t="n">
-        <v>5</v>
+        <v>-3</v>
       </c>
       <c r="AZ38" t="n">
         <v>4</v>
       </c>
       <c r="BA38" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="BB38" t="inlineStr"/>
       <c r="BC38" t="n">
@@ -20007,11 +20007,11 @@
         </is>
       </c>
       <c r="BQ38" t="n">
-        <v>35.8</v>
+        <v>31.8</v>
       </c>
       <c r="BR38" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 35.8% (t(df=4))</t>
+          <t>⚠️ MC survival 31.8% (t(df=4)) ⚠️ HIGH VARIANCE (37.2% vs 26.4% — use caution)</t>
         </is>
       </c>
       <c r="BS38" t="inlineStr">
@@ -20210,10 +20210,10 @@
         <v>1</v>
       </c>
       <c r="EB38" t="n">
-        <v>18.58</v>
+        <v>18.41</v>
       </c>
       <c r="EC38" t="n">
-        <v>0.01</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="39">
@@ -20468,11 +20468,11 @@
         </is>
       </c>
       <c r="BQ39" t="n">
-        <v>70.40000000000001</v>
+        <v>73</v>
       </c>
       <c r="BR39" t="inlineStr">
         <is>
-          <t>✅ MC survival 70.4% (500 sims, 20d, t(df=4))</t>
+          <t>✅ MC survival 73.0% (500 sims, 20d, t(df=4))</t>
         </is>
       </c>
       <c r="BS39" t="inlineStr">
@@ -20671,10 +20671,10 @@
         <v>1</v>
       </c>
       <c r="EB39" t="n">
-        <v>18.58</v>
+        <v>18.41</v>
       </c>
       <c r="EC39" t="n">
-        <v>0.01</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="40">
@@ -20925,11 +20925,11 @@
         </is>
       </c>
       <c r="BQ40" t="n">
-        <v>34.4</v>
+        <v>30.2</v>
       </c>
       <c r="BR40" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 34.4% (t(df=4))</t>
+          <t>⚠️ MC survival 30.2% (t(df=4))</t>
         </is>
       </c>
       <c r="BS40" t="inlineStr">
@@ -21128,10 +21128,10 @@
         <v>1</v>
       </c>
       <c r="EB40" t="n">
-        <v>18.58</v>
+        <v>18.41</v>
       </c>
       <c r="EC40" t="n">
-        <v>0.01</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="41">
@@ -21386,11 +21386,11 @@
         </is>
       </c>
       <c r="BQ41" t="n">
-        <v>41.6</v>
+        <v>40.8</v>
       </c>
       <c r="BR41" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 41.6% (t(df=4))</t>
+          <t>⚠️ MC survival 40.8% (t(df=4))</t>
         </is>
       </c>
       <c r="BS41" t="inlineStr">
@@ -21593,10 +21593,10 @@
         <v>1</v>
       </c>
       <c r="EB41" t="n">
-        <v>18.58</v>
+        <v>18.41</v>
       </c>
       <c r="EC41" t="n">
-        <v>0.01</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="42">
@@ -21847,11 +21847,11 @@
         </is>
       </c>
       <c r="BQ42" t="n">
-        <v>52.6</v>
+        <v>51</v>
       </c>
       <c r="BR42" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 52.6% (t(df=4))</t>
+          <t>⚠️ MC survival 51.0% (t(df=4))</t>
         </is>
       </c>
       <c r="BS42" t="inlineStr">
@@ -22050,10 +22050,10 @@
         <v>1</v>
       </c>
       <c r="EB42" t="n">
-        <v>18.58</v>
+        <v>18.41</v>
       </c>
       <c r="EC42" t="n">
-        <v>0.01</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="43">
@@ -22304,11 +22304,11 @@
         </is>
       </c>
       <c r="BQ43" t="n">
-        <v>35.4</v>
+        <v>37</v>
       </c>
       <c r="BR43" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 35.4% (t(df=4))</t>
+          <t>⚠️ MC survival 37.0% (t(df=4))</t>
         </is>
       </c>
       <c r="BS43" t="inlineStr">
@@ -22515,10 +22515,10 @@
         <v>1</v>
       </c>
       <c r="EB43" t="n">
-        <v>18.58</v>
+        <v>18.41</v>
       </c>
       <c r="EC43" t="n">
-        <v>0.01</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="44">
@@ -22769,11 +22769,11 @@
         </is>
       </c>
       <c r="BQ44" t="n">
-        <v>45.2</v>
+        <v>46.2</v>
       </c>
       <c r="BR44" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 45.2% (t(df=4))</t>
+          <t>⚠️ MC survival 46.2% (t(df=4))</t>
         </is>
       </c>
       <c r="BS44" t="inlineStr">
@@ -22972,10 +22972,10 @@
         <v>1</v>
       </c>
       <c r="EB44" t="n">
-        <v>18.58</v>
+        <v>18.41</v>
       </c>
       <c r="EC44" t="n">
-        <v>0.01</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="45">
@@ -23226,11 +23226,11 @@
         </is>
       </c>
       <c r="BQ45" t="n">
-        <v>31.6</v>
+        <v>28</v>
       </c>
       <c r="BR45" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 31.6% (t(df=4))</t>
+          <t>⚠️ MC survival 28.0% (t(df=4))</t>
         </is>
       </c>
       <c r="BS45" t="inlineStr">
@@ -23429,16 +23429,16 @@
         <v>1</v>
       </c>
       <c r="EB45" t="n">
-        <v>18.58</v>
+        <v>18.41</v>
       </c>
       <c r="EC45" t="n">
-        <v>0.01</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>TATATECH</t>
+          <t>METROPOLIS</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -23447,10 +23447,10 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>622.85</v>
+        <v>540.7</v>
       </c>
       <c r="D46" t="n">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="E46" t="n">
         <v>200</v>
@@ -23466,7 +23466,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="I46" t="n">
         <v>30</v>
@@ -23475,43 +23475,43 @@
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="L46" t="n">
         <v>20</v>
       </c>
       <c r="M46" t="n">
-        <v>642.67</v>
+        <v>495.5</v>
       </c>
       <c r="N46" t="n">
-        <v>653.1900000000001</v>
+        <v>585.26</v>
       </c>
       <c r="O46" t="n">
-        <v>594.53</v>
+        <v>499.11</v>
       </c>
       <c r="P46" t="n">
-        <v>835.47</v>
+        <v>644.15</v>
       </c>
       <c r="Q46" t="n">
-        <v>1028.27</v>
+        <v>792.8</v>
       </c>
       <c r="R46" t="n">
-        <v>1285.34</v>
+        <v>991</v>
       </c>
       <c r="S46" t="n">
-        <v>4.55</v>
+        <v>7.69</v>
       </c>
       <c r="T46" t="n">
-        <v>3.3</v>
+        <v>1.95</v>
       </c>
       <c r="U46" t="n">
-        <v>85.3</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="V46" t="n">
-        <v>62.1</v>
+        <v>69.5</v>
       </c>
       <c r="W46" t="n">
-        <v>54.2</v>
+        <v>53</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -23530,12 +23530,12 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>BELOW</t>
+          <t>ABOVE</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>₹625.97–₹659.53</t>
+          <t>₹473.72–₹514.07</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -23547,13 +23547,13 @@
         <v>1.4</v>
       </c>
       <c r="AE46" t="n">
-        <v>-3.53</v>
+        <v>10.36</v>
       </c>
       <c r="AF46" t="b">
         <v>0</v>
       </c>
       <c r="AG46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH46" t="b">
         <v>1</v>
@@ -23562,7 +23562,7 @@
         <v>1</v>
       </c>
       <c r="AJ46" t="n">
-        <v>48.15</v>
+        <v>160.33</v>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
@@ -23589,7 +23589,7 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>Dividend [SHEETS Tab 4] | ✅ ROE(proxy) 14.6% [ACCEPTABLE] | D/E:23.9</t>
+          <t>Record date [SHEETS Tab 4] | ⚠️ ROE(proxy) unverifiable — filing capped</t>
         </is>
       </c>
       <c r="AQ46" t="inlineStr">
@@ -23599,7 +23599,7 @@
       </c>
       <c r="AR46" t="inlineStr">
         <is>
-          <t>ROE(proxy) 14.6% [ACCEPTABLE] | D/E:23.9</t>
+          <t>ROE quality data unavailable</t>
         </is>
       </c>
       <c r="AS46" t="b">
@@ -23607,30 +23607,26 @@
       </c>
       <c r="AT46" t="inlineStr">
         <is>
-          <t>52W: 21.9% from ₹797 [22% from 52W high] +0pts</t>
+          <t>52W: 9.9% from ₹600 [NEAR 52W HIGH] +5pts</t>
         </is>
       </c>
       <c r="AU46" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AV46" t="inlineStr">
         <is>
-          <t>ATR-V: -0% compressed [EXPANDING]</t>
+          <t>ATR-V: -80% compressed [EXPANDING]</t>
         </is>
       </c>
       <c r="AW46" t="n">
         <v>0</v>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>🌀 VDU 4-bar confirmed (+5pts)</t>
-        </is>
-      </c>
+      <c r="AX46" t="inlineStr"/>
       <c r="AY46" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AZ46" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BA46" t="n">
         <v>5</v>
@@ -23654,25 +23650,25 @@
         </is>
       </c>
       <c r="BH46" t="n">
-        <v>594.53</v>
+        <v>499.11</v>
       </c>
       <c r="BI46" t="inlineStr">
         <is>
-          <t>Initial stop ₹594.53</t>
+          <t>Initial stop ₹499.11</t>
         </is>
       </c>
       <c r="BJ46" t="b">
         <v>0</v>
       </c>
       <c r="BK46" t="n">
-        <v>264</v>
+        <v>180</v>
       </c>
       <c r="BL46" t="n">
-        <v>164432.4</v>
+        <v>97326</v>
       </c>
       <c r="BM46" t="inlineStr">
         <is>
-          <t>264 shares · ₹164,432  (risk ₹7,500)</t>
+          <t>180 shares · ₹97,326  (risk ₹7,500)</t>
         </is>
       </c>
       <c r="BN46" t="n">
@@ -23687,11 +23683,11 @@
         </is>
       </c>
       <c r="BQ46" t="n">
-        <v>49</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="BR46" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 49.0% (t(df=4))</t>
+          <t>✅ MC survival 80.4% (500 sims, 20d, t(df=4))</t>
         </is>
       </c>
       <c r="BS46" t="inlineStr">
@@ -23721,19 +23717,19 @@
       </c>
       <c r="CB46" t="inlineStr"/>
       <c r="CC46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CD46" t="n">
-        <v>8.19</v>
+        <v>14.49</v>
       </c>
       <c r="CE46" t="n">
-        <v>20.23</v>
+        <v>29.71</v>
       </c>
       <c r="CF46" t="n">
-        <v>2582550</v>
+        <v>810023</v>
       </c>
       <c r="CG46" t="n">
-        <v>642.67</v>
+        <v>495.5</v>
       </c>
       <c r="CH46" t="inlineStr">
         <is>
@@ -23742,7 +23738,7 @@
       </c>
       <c r="CI46" t="inlineStr">
         <is>
-          <t>Institutional tide in — fii+dii both accumulating; recent filing: dividend [sheets tab 4] | ✅ roe(proxy) 14.6% [acce</t>
+          <t>Institutional tide in — fii+dii both accumulating; recent filing: record date [sheets tab 4] | ⚠️ roe(proxy) unverif; 2/3 fortress layers at vpoc floor</t>
         </is>
       </c>
       <c r="CJ46" t="b">
@@ -23759,10 +23755,10 @@
         <v>1</v>
       </c>
       <c r="CO46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CP46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CQ46" t="b">
         <v>1</v>
@@ -23771,7 +23767,7 @@
         <v>0</v>
       </c>
       <c r="CS46" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="CT46" t="n">
         <v>0</v>
@@ -23794,7 +23790,7 @@
         <v>39</v>
       </c>
       <c r="CZ46" t="n">
-        <v>683.13</v>
+        <v>554.92</v>
       </c>
       <c r="DA46" t="b">
         <v>0</v>
@@ -23803,23 +23799,23 @@
         <v>0</v>
       </c>
       <c r="DC46" t="n">
-        <v>594.53</v>
+        <v>499.11</v>
       </c>
       <c r="DD46" t="n">
-        <v>594.53</v>
+        <v>499.11</v>
       </c>
       <c r="DE46" t="n">
-        <v>835.47</v>
+        <v>644.15</v>
       </c>
       <c r="DF46" t="n">
-        <v>1028.27</v>
+        <v>792.8</v>
       </c>
       <c r="DG46" t="n">
-        <v>1285.34</v>
+        <v>991</v>
       </c>
       <c r="DH46" t="inlineStr">
         <is>
-          <t>Sell 30% | Move stop to T1 ₹642.67</t>
+          <t>Sell 30% | Move stop to T1 ₹495.50</t>
         </is>
       </c>
       <c r="DI46" t="inlineStr">
@@ -23833,11 +23829,11 @@
         </is>
       </c>
       <c r="DK46" t="n">
-        <v>-3.1</v>
+        <v>9.1</v>
       </c>
       <c r="DL46" t="inlineStr">
         <is>
-          <t>👁️ WATCHING — score 39/100 · -3.1% vs T1</t>
+          <t>👁️ WATCHING — score 39/100 · +9.1% vs T1</t>
         </is>
       </c>
       <c r="DM46" t="inlineStr">
@@ -23879,7 +23875,7 @@
         <v>0</v>
       </c>
       <c r="DY46" t="n">
-        <v>40.46</v>
+        <v>59.42</v>
       </c>
       <c r="DZ46" t="inlineStr">
         <is>
@@ -23890,16 +23886,16 @@
         <v>1</v>
       </c>
       <c r="EB46" t="n">
-        <v>18.58</v>
+        <v>18.41</v>
       </c>
       <c r="EC46" t="n">
-        <v>0.01</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>METROPOLIS</t>
+          <t>TATATECH</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -23908,10 +23904,10 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>540.7</v>
+        <v>622.85</v>
       </c>
       <c r="D47" t="n">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E47" t="n">
         <v>200</v>
@@ -23927,7 +23923,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="I47" t="n">
         <v>30</v>
@@ -23936,43 +23932,43 @@
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L47" t="n">
         <v>20</v>
       </c>
       <c r="M47" t="n">
-        <v>495.5</v>
+        <v>642.67</v>
       </c>
       <c r="N47" t="n">
-        <v>585.26</v>
+        <v>653.1900000000001</v>
       </c>
       <c r="O47" t="n">
-        <v>499.11</v>
+        <v>594.53</v>
       </c>
       <c r="P47" t="n">
-        <v>644.15</v>
+        <v>835.47</v>
       </c>
       <c r="Q47" t="n">
-        <v>792.8</v>
+        <v>1028.27</v>
       </c>
       <c r="R47" t="n">
-        <v>991</v>
+        <v>1285.34</v>
       </c>
       <c r="S47" t="n">
-        <v>7.69</v>
+        <v>4.55</v>
       </c>
       <c r="T47" t="n">
-        <v>1.95</v>
+        <v>3.3</v>
       </c>
       <c r="U47" t="n">
-        <v>94.09999999999999</v>
+        <v>85.3</v>
       </c>
       <c r="V47" t="n">
-        <v>69.5</v>
+        <v>62.1</v>
       </c>
       <c r="W47" t="n">
-        <v>53</v>
+        <v>54.2</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -23991,12 +23987,12 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>ABOVE</t>
+          <t>BELOW</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>₹473.72–₹514.07</t>
+          <t>₹625.97–₹659.53</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
@@ -24008,13 +24004,13 @@
         <v>1.4</v>
       </c>
       <c r="AE47" t="n">
-        <v>10.36</v>
+        <v>-3.53</v>
       </c>
       <c r="AF47" t="b">
         <v>0</v>
       </c>
       <c r="AG47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH47" t="b">
         <v>1</v>
@@ -24023,7 +24019,7 @@
         <v>1</v>
       </c>
       <c r="AJ47" t="n">
-        <v>160.33</v>
+        <v>48.15</v>
       </c>
       <c r="AK47" t="inlineStr">
         <is>
@@ -24050,7 +24046,7 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>Record date [SHEETS Tab 4] | ⚠️ ROE(proxy) unverifiable — filing capped</t>
+          <t>Dividend [SHEETS Tab 4] | ✅ ROE(proxy) 14.6% [ACCEPTABLE] | D/E:23.9</t>
         </is>
       </c>
       <c r="AQ47" t="inlineStr">
@@ -24060,7 +24056,7 @@
       </c>
       <c r="AR47" t="inlineStr">
         <is>
-          <t>ROE quality data unavailable</t>
+          <t>ROE(proxy) 14.6% [ACCEPTABLE] | D/E:23.9</t>
         </is>
       </c>
       <c r="AS47" t="b">
@@ -24068,29 +24064,33 @@
       </c>
       <c r="AT47" t="inlineStr">
         <is>
-          <t>52W: 9.9% from ₹600 [NEAR 52W HIGH] +5pts</t>
+          <t>52W: 21.9% from ₹797 [22% from 52W high] +0pts</t>
         </is>
       </c>
       <c r="AU47" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
-          <t>ATR-V: -80% compressed [EXPANDING]</t>
+          <t>ATR-V: -0% compressed [EXPANDING]</t>
         </is>
       </c>
       <c r="AW47" t="n">
         <v>0</v>
       </c>
-      <c r="AX47" t="inlineStr"/>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>🔴 VDU 4-bar + price drop -1.3% — DISTRIBUTION (-3pts)</t>
+        </is>
+      </c>
       <c r="AY47" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="AZ47" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BA47" t="n">
-        <v>5</v>
+        <v>-3</v>
       </c>
       <c r="BB47" t="inlineStr"/>
       <c r="BC47" t="n">
@@ -24111,25 +24111,25 @@
         </is>
       </c>
       <c r="BH47" t="n">
-        <v>499.11</v>
+        <v>594.53</v>
       </c>
       <c r="BI47" t="inlineStr">
         <is>
-          <t>Initial stop ₹499.11</t>
+          <t>Initial stop ₹594.53</t>
         </is>
       </c>
       <c r="BJ47" t="b">
         <v>0</v>
       </c>
       <c r="BK47" t="n">
-        <v>180</v>
+        <v>264</v>
       </c>
       <c r="BL47" t="n">
-        <v>97326</v>
+        <v>164432.4</v>
       </c>
       <c r="BM47" t="inlineStr">
         <is>
-          <t>180 shares · ₹97,326  (risk ₹7,500)</t>
+          <t>264 shares · ₹164,432  (risk ₹7,500)</t>
         </is>
       </c>
       <c r="BN47" t="n">
@@ -24144,11 +24144,11 @@
         </is>
       </c>
       <c r="BQ47" t="n">
-        <v>80.40000000000001</v>
+        <v>51.8</v>
       </c>
       <c r="BR47" t="inlineStr">
         <is>
-          <t>✅ MC survival 80.4% (500 sims, 20d, t(df=4))</t>
+          <t>⚠️ MC survival 51.8% (t(df=4)) ⚠️ HIGH VARIANCE (57.6% vs 46.0% — use caution)</t>
         </is>
       </c>
       <c r="BS47" t="inlineStr">
@@ -24178,19 +24178,19 @@
       </c>
       <c r="CB47" t="inlineStr"/>
       <c r="CC47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CD47" t="n">
-        <v>14.49</v>
+        <v>8.19</v>
       </c>
       <c r="CE47" t="n">
-        <v>29.71</v>
+        <v>20.23</v>
       </c>
       <c r="CF47" t="n">
-        <v>810023</v>
+        <v>2582550</v>
       </c>
       <c r="CG47" t="n">
-        <v>495.5</v>
+        <v>642.67</v>
       </c>
       <c r="CH47" t="inlineStr">
         <is>
@@ -24199,7 +24199,7 @@
       </c>
       <c r="CI47" t="inlineStr">
         <is>
-          <t>Institutional tide in — fii+dii both accumulating; recent filing: record date [sheets tab 4] | ⚠️ roe(proxy) unverif; 2/3 fortress layers at vpoc floor</t>
+          <t>Institutional tide in — fii+dii both accumulating; recent filing: dividend [sheets tab 4] | ✅ roe(proxy) 14.6% [acce</t>
         </is>
       </c>
       <c r="CJ47" t="b">
@@ -24216,10 +24216,10 @@
         <v>1</v>
       </c>
       <c r="CO47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CP47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CQ47" t="b">
         <v>1</v>
@@ -24228,7 +24228,7 @@
         <v>0</v>
       </c>
       <c r="CS47" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="CT47" t="n">
         <v>0</v>
@@ -24251,7 +24251,7 @@
         <v>39</v>
       </c>
       <c r="CZ47" t="n">
-        <v>554.92</v>
+        <v>683.13</v>
       </c>
       <c r="DA47" t="b">
         <v>0</v>
@@ -24260,23 +24260,23 @@
         <v>0</v>
       </c>
       <c r="DC47" t="n">
-        <v>499.11</v>
+        <v>594.53</v>
       </c>
       <c r="DD47" t="n">
-        <v>499.11</v>
+        <v>594.53</v>
       </c>
       <c r="DE47" t="n">
-        <v>644.15</v>
+        <v>835.47</v>
       </c>
       <c r="DF47" t="n">
-        <v>792.8</v>
+        <v>1028.27</v>
       </c>
       <c r="DG47" t="n">
-        <v>991</v>
+        <v>1285.34</v>
       </c>
       <c r="DH47" t="inlineStr">
         <is>
-          <t>Sell 30% | Move stop to T1 ₹495.50</t>
+          <t>Sell 30% | Move stop to T1 ₹642.67</t>
         </is>
       </c>
       <c r="DI47" t="inlineStr">
@@ -24290,11 +24290,11 @@
         </is>
       </c>
       <c r="DK47" t="n">
-        <v>9.1</v>
+        <v>-3.1</v>
       </c>
       <c r="DL47" t="inlineStr">
         <is>
-          <t>👁️ WATCHING — score 39/100 · +9.1% vs T1</t>
+          <t>👁️ WATCHING — score 39/100 · -3.1% vs T1</t>
         </is>
       </c>
       <c r="DM47" t="inlineStr">
@@ -24336,7 +24336,7 @@
         <v>0</v>
       </c>
       <c r="DY47" t="n">
-        <v>59.42</v>
+        <v>40.46</v>
       </c>
       <c r="DZ47" t="inlineStr">
         <is>
@@ -24347,16 +24347,16 @@
         <v>1</v>
       </c>
       <c r="EB47" t="n">
-        <v>18.58</v>
+        <v>18.41</v>
       </c>
       <c r="EC47" t="n">
-        <v>0.01</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>GRANULES</t>
+          <t>BERGEPAINT</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -24365,10 +24365,10 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>735.3</v>
+        <v>533.9</v>
       </c>
       <c r="D48" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E48" t="n">
         <v>200</v>
@@ -24384,7 +24384,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="I48" t="n">
         <v>30</v>
@@ -24399,37 +24399,37 @@
         <v>20</v>
       </c>
       <c r="M48" t="n">
-        <v>574.03</v>
+        <v>478.28</v>
       </c>
       <c r="N48" t="n">
-        <v>768.97</v>
+        <v>567.6799999999999</v>
       </c>
       <c r="O48" t="n">
-        <v>703.87</v>
+        <v>502.37</v>
       </c>
       <c r="P48" t="n">
-        <v>746.24</v>
+        <v>621.76</v>
       </c>
       <c r="Q48" t="n">
-        <v>918.45</v>
+        <v>765.25</v>
       </c>
       <c r="R48" t="n">
-        <v>1148.06</v>
+        <v>956.5599999999999</v>
       </c>
       <c r="S48" t="n">
-        <v>4.27</v>
+        <v>5.91</v>
       </c>
       <c r="T48" t="n">
-        <v>3.51</v>
+        <v>2.54</v>
       </c>
       <c r="U48" t="n">
-        <v>88</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="V48" t="n">
-        <v>64.09999999999999</v>
+        <v>75.7</v>
       </c>
       <c r="W48" t="n">
-        <v>62.8</v>
+        <v>46.4</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -24453,7 +24453,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>₹560.01–₹588.53</t>
+          <t>₹462.14–₹493.15</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
@@ -24465,13 +24465,13 @@
         <v>1.4</v>
       </c>
       <c r="AE48" t="n">
-        <v>28.9</v>
+        <v>4.48</v>
       </c>
       <c r="AF48" t="b">
         <v>0</v>
       </c>
       <c r="AG48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH48" t="b">
         <v>1</v>
@@ -24480,7 +24480,7 @@
         <v>1</v>
       </c>
       <c r="AJ48" t="n">
-        <v>29.83</v>
+        <v>227.83</v>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
@@ -24525,33 +24525,29 @@
       </c>
       <c r="AT48" t="inlineStr">
         <is>
-          <t>52W: 3.4% from ₹761 [AT 52W HIGH] +9pts</t>
+          <t>52W: 11.8% from ₹605 [APPROACHING HIGH] +3pts</t>
         </is>
       </c>
       <c r="AU48" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AV48" t="inlineStr">
         <is>
-          <t>ATR-V: -1% compressed [EXPANDING]</t>
+          <t>ATR-V: -67% compressed [EXPANDING]</t>
         </is>
       </c>
       <c r="AW48" t="n">
         <v>0</v>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>🌀 VDU 4-bar confirmed (+5pts)</t>
-        </is>
-      </c>
+      <c r="AX48" t="inlineStr"/>
       <c r="AY48" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AZ48" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BA48" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="BB48" t="inlineStr"/>
       <c r="BC48" t="n">
@@ -24572,25 +24568,25 @@
         </is>
       </c>
       <c r="BH48" t="n">
-        <v>703.87</v>
+        <v>502.37</v>
       </c>
       <c r="BI48" t="inlineStr">
         <is>
-          <t>Initial stop ₹703.87</t>
+          <t>Initial stop ₹502.37</t>
         </is>
       </c>
       <c r="BJ48" t="b">
         <v>0</v>
       </c>
       <c r="BK48" t="n">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="BL48" t="n">
-        <v>175001.4</v>
+        <v>126534.3</v>
       </c>
       <c r="BM48" t="inlineStr">
         <is>
-          <t>238 shares · ₹175,001  (risk ₹7,500)</t>
+          <t>237 shares · ₹126,534  (risk ₹7,500)</t>
         </is>
       </c>
       <c r="BN48" t="n">
@@ -24605,11 +24601,11 @@
         </is>
       </c>
       <c r="BQ48" t="n">
-        <v>61.4</v>
+        <v>67.8</v>
       </c>
       <c r="BR48" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 61.4% (t(df=4))</t>
+          <t>⚠️ MC survival 67.8% (t(df=4))</t>
         </is>
       </c>
       <c r="BS48" t="inlineStr">
@@ -24631,27 +24627,31 @@
         </is>
       </c>
       <c r="BY48" t="b">
-        <v>0</v>
-      </c>
-      <c r="BZ48" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="BZ48" t="inlineStr">
+        <is>
+          <t>⚠️ EXHAUSTION_WARNING — RSI 75.7&gt;75 · Vol climax 4.6×ADV</t>
+        </is>
+      </c>
       <c r="CA48" t="b">
         <v>0</v>
       </c>
       <c r="CB48" t="inlineStr"/>
       <c r="CC48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CD48" t="n">
-        <v>12.95</v>
+        <v>13.09</v>
       </c>
       <c r="CE48" t="n">
-        <v>22.45</v>
+        <v>22.52</v>
       </c>
       <c r="CF48" t="n">
-        <v>1677968</v>
+        <v>927490</v>
       </c>
       <c r="CG48" t="n">
-        <v>574.03</v>
+        <v>478.28</v>
       </c>
       <c r="CH48" t="inlineStr">
         <is>
@@ -24660,7 +24660,7 @@
       </c>
       <c r="CI48" t="inlineStr">
         <is>
-          <t>Institutional tide in — fii+dii both accumulating; recent filing: analysts/institutional investor meet/con. call upd</t>
+          <t>Institutional tide in — fii+dii both accumulating; recent filing: analysts/institutional investor meet/con. call upd; 2/3 fortress layers at vpoc floor</t>
         </is>
       </c>
       <c r="CJ48" t="b">
@@ -24677,7 +24677,7 @@
         <v>1</v>
       </c>
       <c r="CO48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CP48" t="b">
         <v>1</v>
@@ -24689,7 +24689,7 @@
         <v>0</v>
       </c>
       <c r="CS48" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="CT48" t="n">
         <v>0</v>
@@ -24712,32 +24712,32 @@
         <v>39</v>
       </c>
       <c r="CZ48" t="n">
-        <v>618.9299999999999</v>
+        <v>523.3200000000001</v>
       </c>
       <c r="DA48" t="b">
         <v>1</v>
       </c>
       <c r="DB48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DC48" t="n">
-        <v>703.87</v>
+        <v>502.37</v>
       </c>
       <c r="DD48" t="n">
-        <v>703.87</v>
+        <v>502.37</v>
       </c>
       <c r="DE48" t="n">
-        <v>746.24</v>
+        <v>621.76</v>
       </c>
       <c r="DF48" t="n">
-        <v>918.45</v>
+        <v>765.25</v>
       </c>
       <c r="DG48" t="n">
-        <v>1148.06</v>
+        <v>956.5599999999999</v>
       </c>
       <c r="DH48" t="inlineStr">
         <is>
-          <t>Sell 30% | Move stop to T1 ₹574.03</t>
+          <t>Sell 30% | Move stop to T1 ₹478.28</t>
         </is>
       </c>
       <c r="DI48" t="inlineStr">
@@ -24751,11 +24751,11 @@
         </is>
       </c>
       <c r="DK48" t="n">
-        <v>28.1</v>
+        <v>11.6</v>
       </c>
       <c r="DL48" t="inlineStr">
         <is>
-          <t>👁️ WATCHING — score 39/100 · +28.1% vs T1</t>
+          <t>👁️ WATCHING — score 39/100 · +11.6% vs T1</t>
         </is>
       </c>
       <c r="DM48" t="inlineStr">
@@ -24797,7 +24797,7 @@
         <v>0</v>
       </c>
       <c r="DY48" t="n">
-        <v>44.9</v>
+        <v>45.04</v>
       </c>
       <c r="DZ48" t="inlineStr">
         <is>
@@ -24808,16 +24808,16 @@
         <v>1</v>
       </c>
       <c r="EB48" t="n">
-        <v>18.58</v>
+        <v>18.41</v>
       </c>
       <c r="EC48" t="n">
-        <v>0.01</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BERGEPAINT</t>
+          <t>GRANULES</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -24826,10 +24826,10 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>533.9</v>
+        <v>735.3</v>
       </c>
       <c r="D49" t="n">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="E49" t="n">
         <v>200</v>
@@ -24845,7 +24845,7 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="I49" t="n">
         <v>30</v>
@@ -24860,37 +24860,37 @@
         <v>20</v>
       </c>
       <c r="M49" t="n">
-        <v>478.28</v>
+        <v>574.03</v>
       </c>
       <c r="N49" t="n">
-        <v>567.6799999999999</v>
+        <v>768.97</v>
       </c>
       <c r="O49" t="n">
-        <v>502.37</v>
+        <v>703.87</v>
       </c>
       <c r="P49" t="n">
-        <v>621.76</v>
+        <v>746.24</v>
       </c>
       <c r="Q49" t="n">
-        <v>765.25</v>
+        <v>918.45</v>
       </c>
       <c r="R49" t="n">
-        <v>956.5599999999999</v>
+        <v>1148.06</v>
       </c>
       <c r="S49" t="n">
-        <v>5.91</v>
+        <v>4.27</v>
       </c>
       <c r="T49" t="n">
-        <v>2.54</v>
+        <v>3.51</v>
       </c>
       <c r="U49" t="n">
-        <v>94.90000000000001</v>
+        <v>88</v>
       </c>
       <c r="V49" t="n">
-        <v>75.7</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="W49" t="n">
-        <v>46.4</v>
+        <v>62.8</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -24914,7 +24914,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>₹462.14–₹493.15</t>
+          <t>₹560.01–₹588.53</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
@@ -24926,13 +24926,13 @@
         <v>1.4</v>
       </c>
       <c r="AE49" t="n">
-        <v>4.48</v>
+        <v>28.9</v>
       </c>
       <c r="AF49" t="b">
         <v>0</v>
       </c>
       <c r="AG49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH49" t="b">
         <v>1</v>
@@ -24941,7 +24941,7 @@
         <v>1</v>
       </c>
       <c r="AJ49" t="n">
-        <v>227.83</v>
+        <v>29.83</v>
       </c>
       <c r="AK49" t="inlineStr">
         <is>
@@ -24986,29 +24986,33 @@
       </c>
       <c r="AT49" t="inlineStr">
         <is>
-          <t>52W: 11.8% from ₹605 [APPROACHING HIGH] +3pts</t>
+          <t>52W: 3.4% from ₹761 [AT 52W HIGH] +9pts</t>
         </is>
       </c>
       <c r="AU49" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
-          <t>ATR-V: -67% compressed [EXPANDING]</t>
+          <t>ATR-V: -1% compressed [EXPANDING]</t>
         </is>
       </c>
       <c r="AW49" t="n">
         <v>0</v>
       </c>
-      <c r="AX49" t="inlineStr"/>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>🔴 VDU 4-bar + price drop -2.3% — DISTRIBUTION (-3pts)</t>
+        </is>
+      </c>
       <c r="AY49" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="AZ49" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BA49" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BB49" t="inlineStr"/>
       <c r="BC49" t="n">
@@ -25029,25 +25033,25 @@
         </is>
       </c>
       <c r="BH49" t="n">
-        <v>502.37</v>
+        <v>703.87</v>
       </c>
       <c r="BI49" t="inlineStr">
         <is>
-          <t>Initial stop ₹502.37</t>
+          <t>Initial stop ₹703.87</t>
         </is>
       </c>
       <c r="BJ49" t="b">
         <v>0</v>
       </c>
       <c r="BK49" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="BL49" t="n">
-        <v>126534.3</v>
+        <v>175001.4</v>
       </c>
       <c r="BM49" t="inlineStr">
         <is>
-          <t>237 shares · ₹126,534  (risk ₹7,500)</t>
+          <t>238 shares · ₹175,001  (risk ₹7,500)</t>
         </is>
       </c>
       <c r="BN49" t="n">
@@ -25062,11 +25066,11 @@
         </is>
       </c>
       <c r="BQ49" t="n">
-        <v>66.2</v>
+        <v>59.2</v>
       </c>
       <c r="BR49" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 66.2% (t(df=4))</t>
+          <t>⚠️ MC survival 59.2% (t(df=4))</t>
         </is>
       </c>
       <c r="BS49" t="inlineStr">
@@ -25088,31 +25092,27 @@
         </is>
       </c>
       <c r="BY49" t="b">
-        <v>1</v>
-      </c>
-      <c r="BZ49" t="inlineStr">
-        <is>
-          <t>⚠️ EXHAUSTION_WARNING — RSI 75.7&gt;75 · Vol climax 4.6×ADV</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="BZ49" t="inlineStr"/>
       <c r="CA49" t="b">
         <v>0</v>
       </c>
       <c r="CB49" t="inlineStr"/>
       <c r="CC49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CD49" t="n">
-        <v>13.09</v>
+        <v>12.95</v>
       </c>
       <c r="CE49" t="n">
-        <v>22.52</v>
+        <v>22.45</v>
       </c>
       <c r="CF49" t="n">
-        <v>927490</v>
+        <v>1677968</v>
       </c>
       <c r="CG49" t="n">
-        <v>478.28</v>
+        <v>574.03</v>
       </c>
       <c r="CH49" t="inlineStr">
         <is>
@@ -25121,7 +25121,7 @@
       </c>
       <c r="CI49" t="inlineStr">
         <is>
-          <t>Institutional tide in — fii+dii both accumulating; recent filing: analysts/institutional investor meet/con. call upd; 2/3 fortress layers at vpoc floor</t>
+          <t>Institutional tide in — fii+dii both accumulating; recent filing: analysts/institutional investor meet/con. call upd</t>
         </is>
       </c>
       <c r="CJ49" t="b">
@@ -25138,7 +25138,7 @@
         <v>1</v>
       </c>
       <c r="CO49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CP49" t="b">
         <v>1</v>
@@ -25150,7 +25150,7 @@
         <v>0</v>
       </c>
       <c r="CS49" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="CT49" t="n">
         <v>0</v>
@@ -25173,32 +25173,32 @@
         <v>39</v>
       </c>
       <c r="CZ49" t="n">
-        <v>523.3200000000001</v>
+        <v>618.9299999999999</v>
       </c>
       <c r="DA49" t="b">
         <v>1</v>
       </c>
       <c r="DB49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DC49" t="n">
-        <v>502.37</v>
+        <v>703.87</v>
       </c>
       <c r="DD49" t="n">
-        <v>502.37</v>
+        <v>703.87</v>
       </c>
       <c r="DE49" t="n">
-        <v>621.76</v>
+        <v>746.24</v>
       </c>
       <c r="DF49" t="n">
-        <v>765.25</v>
+        <v>918.45</v>
       </c>
       <c r="DG49" t="n">
-        <v>956.5599999999999</v>
+        <v>1148.06</v>
       </c>
       <c r="DH49" t="inlineStr">
         <is>
-          <t>Sell 30% | Move stop to T1 ₹478.28</t>
+          <t>Sell 30% | Move stop to T1 ₹574.03</t>
         </is>
       </c>
       <c r="DI49" t="inlineStr">
@@ -25212,11 +25212,11 @@
         </is>
       </c>
       <c r="DK49" t="n">
-        <v>11.6</v>
+        <v>28.1</v>
       </c>
       <c r="DL49" t="inlineStr">
         <is>
-          <t>👁️ WATCHING — score 39/100 · +11.6% vs T1</t>
+          <t>👁️ WATCHING — score 39/100 · +28.1% vs T1</t>
         </is>
       </c>
       <c r="DM49" t="inlineStr">
@@ -25258,7 +25258,7 @@
         <v>0</v>
       </c>
       <c r="DY49" t="n">
-        <v>45.04</v>
+        <v>44.9</v>
       </c>
       <c r="DZ49" t="inlineStr">
         <is>
@@ -25269,10 +25269,10 @@
         <v>1</v>
       </c>
       <c r="EB49" t="n">
-        <v>18.58</v>
+        <v>18.41</v>
       </c>
       <c r="EC49" t="n">
-        <v>0.01</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="50">
@@ -25523,11 +25523,11 @@
         </is>
       </c>
       <c r="BQ50" t="n">
-        <v>64.8</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="BR50" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 64.8% (t(df=4))</t>
+          <t>⚠️ MC survival 69.6% (t(df=4))</t>
         </is>
       </c>
       <c r="BS50" t="inlineStr">
@@ -25730,10 +25730,10 @@
         <v>1</v>
       </c>
       <c r="EB50" t="n">
-        <v>18.58</v>
+        <v>18.41</v>
       </c>
       <c r="EC50" t="n">
-        <v>0.01</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="51">
@@ -25984,11 +25984,11 @@
         </is>
       </c>
       <c r="BQ51" t="n">
-        <v>47.8</v>
+        <v>52.2</v>
       </c>
       <c r="BR51" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 47.8% (t(df=4))</t>
+          <t>⚠️ MC survival 52.2% (t(df=4))</t>
         </is>
       </c>
       <c r="BS51" t="inlineStr">
@@ -26195,10 +26195,10 @@
         <v>1</v>
       </c>
       <c r="EB51" t="n">
-        <v>18.58</v>
+        <v>18.41</v>
       </c>
       <c r="EC51" t="n">
-        <v>0.01</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="52">
@@ -26449,11 +26449,11 @@
         </is>
       </c>
       <c r="BQ52" t="n">
-        <v>41.6</v>
+        <v>41.2</v>
       </c>
       <c r="BR52" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 41.6% (t(df=4))</t>
+          <t>⚠️ MC survival 41.2% (t(df=4))</t>
         </is>
       </c>
       <c r="BS52" t="inlineStr">
@@ -26652,10 +26652,10 @@
         <v>1</v>
       </c>
       <c r="EB52" t="n">
-        <v>18.58</v>
+        <v>18.41</v>
       </c>
       <c r="EC52" t="n">
-        <v>0.01</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="53">
@@ -26906,11 +26906,11 @@
         </is>
       </c>
       <c r="BQ53" t="n">
-        <v>39.2</v>
+        <v>39</v>
       </c>
       <c r="BR53" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 39.2% (t(df=4))</t>
+          <t>⚠️ MC survival 39.0% (t(df=4))</t>
         </is>
       </c>
       <c r="BS53" t="inlineStr">
@@ -27109,10 +27109,10 @@
         <v>1</v>
       </c>
       <c r="EB53" t="n">
-        <v>18.58</v>
+        <v>18.41</v>
       </c>
       <c r="EC53" t="n">
-        <v>0.01</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="54">
@@ -27367,11 +27367,11 @@
         </is>
       </c>
       <c r="BQ54" t="n">
-        <v>51.6</v>
+        <v>53.6</v>
       </c>
       <c r="BR54" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 51.6% (t(df=4))</t>
+          <t>⚠️ MC survival 53.6% (t(df=4)) ⚠️ HIGH VARIANCE (58.8% vs 48.4% — use caution)</t>
         </is>
       </c>
       <c r="BS54" t="inlineStr">
@@ -27570,10 +27570,10 @@
         <v>1</v>
       </c>
       <c r="EB54" t="n">
-        <v>18.58</v>
+        <v>18.41</v>
       </c>
       <c r="EC54" t="n">
-        <v>0.01</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="55">
@@ -27628,7 +27628,7 @@
         <v>227.98</v>
       </c>
       <c r="O55" t="n">
-        <v>216.56</v>
+        <v>215.65</v>
       </c>
       <c r="P55" t="n">
         <v>254.27</v>
@@ -27640,10 +27640,10 @@
         <v>391.18</v>
       </c>
       <c r="S55" t="n">
-        <v>2.07</v>
+        <v>2.48</v>
       </c>
       <c r="T55" t="n">
-        <v>7.26</v>
+        <v>6.05</v>
       </c>
       <c r="U55" t="n">
         <v>68.90000000000001</v>
@@ -27681,11 +27681,11 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>ATR-1.00× stop</t>
+          <t>ATR-1.20× stop</t>
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AE55" t="n">
         <v>21</v>
@@ -27795,25 +27795,25 @@
         </is>
       </c>
       <c r="BH55" t="n">
-        <v>216.56</v>
+        <v>215.65</v>
       </c>
       <c r="BI55" t="inlineStr">
         <is>
-          <t>Initial stop ₹216.56</t>
+          <t>Initial stop ₹215.65</t>
         </is>
       </c>
       <c r="BJ55" t="b">
         <v>0</v>
       </c>
       <c r="BK55" t="n">
-        <v>1641</v>
+        <v>1367</v>
       </c>
       <c r="BL55" t="n">
-        <v>362874.33</v>
+        <v>302284.71</v>
       </c>
       <c r="BM55" t="inlineStr">
         <is>
-          <t>1641 shares · ₹362,874  (risk ₹7,500)</t>
+          <t>1367 shares · ₹302,285  (risk ₹7,500)</t>
         </is>
       </c>
       <c r="BN55" t="n">
@@ -27828,11 +27828,11 @@
         </is>
       </c>
       <c r="BQ55" t="n">
-        <v>43.8</v>
+        <v>48.2</v>
       </c>
       <c r="BR55" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 43.8% (t(df=4))</t>
+          <t>⚠️ MC survival 48.2% (t(df=4))</t>
         </is>
       </c>
       <c r="BS55" t="inlineStr">
@@ -27948,10 +27948,10 @@
         <v>0</v>
       </c>
       <c r="DC55" t="n">
-        <v>216.56</v>
+        <v>215.65</v>
       </c>
       <c r="DD55" t="n">
-        <v>216.56</v>
+        <v>215.65</v>
       </c>
       <c r="DE55" t="n">
         <v>254.27</v>
@@ -28035,10 +28035,10 @@
         <v>1</v>
       </c>
       <c r="EB55" t="n">
-        <v>18.58</v>
+        <v>18.41</v>
       </c>
       <c r="EC55" t="n">
-        <v>0.01</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="56">
@@ -28093,7 +28093,7 @@
         <v>97.05</v>
       </c>
       <c r="O56" t="n">
-        <v>91.29000000000001</v>
+        <v>90.91</v>
       </c>
       <c r="P56" t="n">
         <v>101.88</v>
@@ -28105,10 +28105,10 @@
         <v>156.74</v>
       </c>
       <c r="S56" t="n">
-        <v>2.06</v>
+        <v>2.47</v>
       </c>
       <c r="T56" t="n">
-        <v>7.28</v>
+        <v>6.08</v>
       </c>
       <c r="U56" t="n">
         <v>69</v>
@@ -28146,11 +28146,11 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>ATR-0.75× stop</t>
+          <t>ATR-0.90× stop</t>
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="AE56" t="n">
         <v>18.68</v>
@@ -28256,25 +28256,25 @@
         </is>
       </c>
       <c r="BH56" t="n">
-        <v>91.29000000000001</v>
+        <v>90.91</v>
       </c>
       <c r="BI56" t="inlineStr">
         <is>
-          <t>Initial stop ₹91.29</t>
+          <t>Initial stop ₹90.91</t>
         </is>
       </c>
       <c r="BJ56" t="b">
         <v>0</v>
       </c>
       <c r="BK56" t="n">
-        <v>3906</v>
+        <v>3255</v>
       </c>
       <c r="BL56" t="n">
-        <v>364078.26</v>
+        <v>303398.55</v>
       </c>
       <c r="BM56" t="inlineStr">
         <is>
-          <t>3906 shares · ₹364,078  (risk ₹7,500)</t>
+          <t>3255 shares · ₹303,399  (risk ₹7,500)</t>
         </is>
       </c>
       <c r="BN56" t="n">
@@ -28289,11 +28289,11 @@
         </is>
       </c>
       <c r="BQ56" t="n">
-        <v>39.8</v>
+        <v>45.8</v>
       </c>
       <c r="BR56" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 39.8% (t(df=4))</t>
+          <t>⚠️ MC survival 45.8% (t(df=4))</t>
         </is>
       </c>
       <c r="BS56" t="inlineStr">
@@ -28405,10 +28405,10 @@
         <v>1</v>
       </c>
       <c r="DC56" t="n">
-        <v>91.29000000000001</v>
+        <v>90.91</v>
       </c>
       <c r="DD56" t="n">
-        <v>91.29000000000001</v>
+        <v>90.91</v>
       </c>
       <c r="DE56" t="n">
         <v>101.88</v>
@@ -28492,10 +28492,10 @@
         <v>1</v>
       </c>
       <c r="EB56" t="n">
-        <v>18.58</v>
+        <v>18.41</v>
       </c>
       <c r="EC56" t="n">
-        <v>0.01</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="57">
@@ -28746,11 +28746,11 @@
         </is>
       </c>
       <c r="BQ57" t="n">
-        <v>25</v>
+        <v>26.4</v>
       </c>
       <c r="BR57" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 25.0% (t(df=4))</t>
+          <t>⚠️ MC survival 26.4% (t(df=4))</t>
         </is>
       </c>
       <c r="BS57" t="inlineStr">
@@ -28949,10 +28949,10 @@
         <v>1</v>
       </c>
       <c r="EB57" t="n">
-        <v>18.58</v>
+        <v>18.41</v>
       </c>
       <c r="EC57" t="n">
-        <v>0.01</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="58">
@@ -29203,11 +29203,11 @@
         </is>
       </c>
       <c r="BQ58" t="n">
-        <v>67.2</v>
+        <v>64.8</v>
       </c>
       <c r="BR58" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 67.2% (t(df=4))</t>
+          <t>⚠️ MC survival 64.8% (t(df=4))</t>
         </is>
       </c>
       <c r="BS58" t="inlineStr">
@@ -29406,16 +29406,16 @@
         <v>1</v>
       </c>
       <c r="EB58" t="n">
-        <v>18.58</v>
+        <v>18.41</v>
       </c>
       <c r="EC58" t="n">
-        <v>0.01</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SCI</t>
+          <t>GKENERGY</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -29424,10 +29424,10 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>326.9</v>
+        <v>129.24</v>
       </c>
       <c r="D59" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E59" t="n">
         <v>200</v>
@@ -29443,7 +29443,7 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I59" t="n">
         <v>30</v>
@@ -29458,37 +29458,37 @@
         <v>20</v>
       </c>
       <c r="M59" t="n">
-        <v>276.35</v>
+        <v>139.22</v>
       </c>
       <c r="N59" t="n">
-        <v>355.01</v>
+        <v>140.5</v>
       </c>
       <c r="O59" t="n">
-        <v>300.66</v>
+        <v>121.73</v>
       </c>
       <c r="P59" t="n">
-        <v>359.26</v>
+        <v>180.99</v>
       </c>
       <c r="Q59" t="n">
-        <v>442.16</v>
+        <v>222.75</v>
       </c>
       <c r="R59" t="n">
-        <v>552.7</v>
+        <v>278.44</v>
       </c>
       <c r="S59" t="n">
-        <v>8.029999999999999</v>
+        <v>5.81</v>
       </c>
       <c r="T59" t="n">
-        <v>1.87</v>
+        <v>2.58</v>
       </c>
       <c r="U59" t="n">
-        <v>80.7</v>
+        <v>61.4</v>
       </c>
       <c r="V59" t="n">
-        <v>59.9</v>
+        <v>54</v>
       </c>
       <c r="W59" t="n">
-        <v>48.2</v>
+        <v>27.4</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -29507,24 +29507,24 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>ABOVE</t>
+          <t>BELOW</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>₹263.67–₹287.04</t>
+          <t>₹132.75–₹144.65</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>ATR-1.40× stop</t>
+          <t>ATR-1.00× stop</t>
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="AE59" t="n">
-        <v>36.7</v>
+        <v>5.01</v>
       </c>
       <c r="AF59" t="b">
         <v>0</v>
@@ -29539,11 +29539,11 @@
         <v>1</v>
       </c>
       <c r="AJ59" t="n">
-        <v>219.99</v>
+        <v>25.16</v>
       </c>
       <c r="AK59" t="inlineStr">
         <is>
-          <t>MA200</t>
+          <t>MA100</t>
         </is>
       </c>
       <c r="AL59" t="n">
@@ -29566,7 +29566,7 @@
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>Dividend [SHEETS Tab 4] | ⚠️ ROE(proxy) unverifiable — filing capped</t>
+          <t>Awarding of order(s)/contract(s) [SHEETS Tab 4] | ⚠️ ROE(proxy) unverifiable — filing capped</t>
         </is>
       </c>
       <c r="AQ59" t="inlineStr">
@@ -29584,33 +29584,29 @@
       </c>
       <c r="AT59" t="inlineStr">
         <is>
-          <t>52W: 11.3% from ₹369 [APPROACHING HIGH] +3pts</t>
+          <t>52W: 46.1% from ₹240 [46% from 52W high] +0pts</t>
         </is>
       </c>
       <c r="AU59" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
-          <t>ATR-V: -35% compressed [EXPANDING]</t>
+          <t>ATR-V: -17% compressed [EXPANDING]</t>
         </is>
       </c>
       <c r="AW59" t="n">
         <v>0</v>
       </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>🌀 VDU 4-bar confirmed (+5pts)</t>
-        </is>
-      </c>
+      <c r="AX59" t="inlineStr"/>
       <c r="AY59" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AZ59" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BA59" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BB59" t="inlineStr"/>
       <c r="BC59" t="n">
@@ -29631,25 +29627,25 @@
         </is>
       </c>
       <c r="BH59" t="n">
-        <v>300.66</v>
+        <v>121.73</v>
       </c>
       <c r="BI59" t="inlineStr">
         <is>
-          <t>Initial stop ₹300.66</t>
+          <t>Initial stop ₹121.73</t>
         </is>
       </c>
       <c r="BJ59" t="b">
         <v>0</v>
       </c>
       <c r="BK59" t="n">
-        <v>285</v>
+        <v>998</v>
       </c>
       <c r="BL59" t="n">
-        <v>93166.5</v>
+        <v>128981.52</v>
       </c>
       <c r="BM59" t="inlineStr">
         <is>
-          <t>285 shares · ₹93,166  (risk ₹7,500)</t>
+          <t>998 shares · ₹128,982  (risk ₹7,500)</t>
         </is>
       </c>
       <c r="BN59" t="n">
@@ -29664,19 +29660,23 @@
         </is>
       </c>
       <c r="BQ59" t="n">
-        <v>68.59999999999999</v>
+        <v>32.6</v>
       </c>
       <c r="BR59" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 68.6% (t(df=4))</t>
+          <t>⚠️ MC survival 32.6% (t(df=4))</t>
         </is>
       </c>
       <c r="BS59" t="inlineStr">
         <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="BT59" t="inlineStr"/>
+          <t>ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="BT59" t="inlineStr">
+        <is>
+          <t>🟢 CVD Accum — smart money</t>
+        </is>
+      </c>
       <c r="BU59" t="b">
         <v>0</v>
       </c>
@@ -29698,19 +29698,19 @@
       </c>
       <c r="CB59" t="inlineStr"/>
       <c r="CC59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CD59" t="n">
-        <v>13.14</v>
+        <v>7.47</v>
       </c>
       <c r="CE59" t="n">
-        <v>18.74</v>
+        <v>7.51</v>
       </c>
       <c r="CF59" t="n">
-        <v>18376034</v>
+        <v>1131450</v>
       </c>
       <c r="CG59" t="n">
-        <v>276.35</v>
+        <v>139.22</v>
       </c>
       <c r="CH59" t="inlineStr">
         <is>
@@ -29719,17 +29719,13 @@
       </c>
       <c r="CI59" t="inlineStr">
         <is>
-          <t>Institutional tide in — fii+dii both accumulating; recent filing: dividend [sheets tab 4] | ⚠️ roe(proxy) unverifiab</t>
+          <t xml:space="preserve">Institutional tide in — fii+dii both accumulating; recent filing: awarding of order(s)/contract(s) [sheets tab 4] | </t>
         </is>
       </c>
       <c r="CJ59" t="b">
-        <v>1</v>
-      </c>
-      <c r="CK59" t="inlineStr">
-        <is>
-          <t>⚠️ ROUND_TRIP_RISK — close 327 &lt; 90% of 369</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="CK59" t="inlineStr"/>
       <c r="CL59" t="b">
         <v>0</v>
       </c>
@@ -29743,7 +29739,7 @@
         <v>0</v>
       </c>
       <c r="CP59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CQ59" t="b">
         <v>1</v>
@@ -29752,55 +29748,55 @@
         <v>0</v>
       </c>
       <c r="CS59" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="CT59" t="n">
         <v>0</v>
       </c>
       <c r="CU59" t="n">
-        <v>0.068</v>
+        <v>0.215</v>
       </c>
       <c r="CV59" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="CW59" t="n">
         <v>-5</v>
       </c>
       <c r="CX59" t="inlineStr">
         <is>
-          <t>🧠 Sniper Bayes 7% — LOW</t>
+          <t>🧠 Sniper Bayes 22% — LOW</t>
         </is>
       </c>
       <c r="CY59" t="n">
         <v>30</v>
       </c>
       <c r="CZ59" t="n">
-        <v>313.83</v>
+        <v>154.24</v>
       </c>
       <c r="DA59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DB59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DC59" t="n">
-        <v>300.66</v>
+        <v>121.73</v>
       </c>
       <c r="DD59" t="n">
-        <v>300.66</v>
+        <v>121.73</v>
       </c>
       <c r="DE59" t="n">
-        <v>359.26</v>
+        <v>180.99</v>
       </c>
       <c r="DF59" t="n">
-        <v>442.16</v>
+        <v>222.75</v>
       </c>
       <c r="DG59" t="n">
-        <v>552.7</v>
+        <v>278.44</v>
       </c>
       <c r="DH59" t="inlineStr">
         <is>
-          <t>Sell 30% | Move stop to T1 ₹276.35</t>
+          <t>Sell 30% | Move stop to T1 ₹139.22</t>
         </is>
       </c>
       <c r="DI59" t="inlineStr">
@@ -29814,11 +29810,11 @@
         </is>
       </c>
       <c r="DK59" t="n">
-        <v>18.3</v>
+        <v>-7.2</v>
       </c>
       <c r="DL59" t="inlineStr">
         <is>
-          <t>👁️ WATCHING — score 30/100 · +18.3% vs T1</t>
+          <t>👁️ WATCHING — score 30/100 · -7.2% vs T1</t>
         </is>
       </c>
       <c r="DM59" t="inlineStr">
@@ -29860,7 +29856,7 @@
         <v>0</v>
       </c>
       <c r="DY59" t="n">
-        <v>37.48</v>
+        <v>15.02</v>
       </c>
       <c r="DZ59" t="inlineStr">
         <is>
@@ -29871,16 +29867,16 @@
         <v>1</v>
       </c>
       <c r="EB59" t="n">
-        <v>18.58</v>
+        <v>18.41</v>
       </c>
       <c r="EC59" t="n">
-        <v>0.01</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>GKENERGY</t>
+          <t>TALBROAUTO</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -29889,7 +29885,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>129.24</v>
+        <v>327.25</v>
       </c>
       <c r="D60" t="n">
         <v>85</v>
@@ -29908,7 +29904,7 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I60" t="n">
         <v>30</v>
@@ -29917,43 +29913,43 @@
         <v>0</v>
       </c>
       <c r="K60" t="n">
+        <v>15</v>
+      </c>
+      <c r="L60" t="n">
         <v>10</v>
       </c>
-      <c r="L60" t="n">
-        <v>20</v>
-      </c>
       <c r="M60" t="n">
-        <v>139.22</v>
+        <v>296.42</v>
       </c>
       <c r="N60" t="n">
-        <v>140.5</v>
+        <v>356.49</v>
       </c>
       <c r="O60" t="n">
-        <v>121.73</v>
+        <v>299.96</v>
       </c>
       <c r="P60" t="n">
-        <v>180.99</v>
+        <v>385.35</v>
       </c>
       <c r="Q60" t="n">
-        <v>222.75</v>
+        <v>474.27</v>
       </c>
       <c r="R60" t="n">
-        <v>278.44</v>
+        <v>592.84</v>
       </c>
       <c r="S60" t="n">
-        <v>5.81</v>
+        <v>8.34</v>
       </c>
       <c r="T60" t="n">
-        <v>2.58</v>
+        <v>1.8</v>
       </c>
       <c r="U60" t="n">
-        <v>61.4</v>
+        <v>85</v>
       </c>
       <c r="V60" t="n">
-        <v>54</v>
+        <v>57.9</v>
       </c>
       <c r="W60" t="n">
-        <v>27.4</v>
+        <v>63.8</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -29972,24 +29968,24 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>BELOW</t>
+          <t>ABOVE</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>₹132.75–₹144.65</t>
+          <t>₹282.30–₹308.21</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>ATR-1.00× stop</t>
+          <t>ATR-1.40× stop</t>
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AE60" t="n">
-        <v>5.01</v>
+        <v>17.8</v>
       </c>
       <c r="AF60" t="b">
         <v>0</v>
@@ -30004,11 +30000,11 @@
         <v>1</v>
       </c>
       <c r="AJ60" t="n">
-        <v>25.16</v>
+        <v>3.52</v>
       </c>
       <c r="AK60" t="inlineStr">
         <is>
-          <t>MA100</t>
+          <t>MA200</t>
         </is>
       </c>
       <c r="AL60" t="n">
@@ -30031,17 +30027,17 @@
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>Awarding of order(s)/contract(s) [SHEETS Tab 4] | ⚠️ ROE(proxy) unverifiable — filing capped</t>
+          <t>Analysts/institutional investor meet/con. call updates [SHEETS Tab 4]</t>
         </is>
       </c>
       <c r="AQ60" t="inlineStr">
         <is>
-          <t>No result date found (neutral)</t>
+          <t>⚠️ Results in 4td — risky, size to PROBE</t>
         </is>
       </c>
       <c r="AR60" t="inlineStr">
         <is>
-          <t>ROE quality data unavailable</t>
+          <t>Not checked</t>
         </is>
       </c>
       <c r="AS60" t="b">
@@ -30049,15 +30045,15 @@
       </c>
       <c r="AT60" t="inlineStr">
         <is>
-          <t>52W: 46.1% from ₹240 [46% from 52W high] +0pts</t>
+          <t>52W: 6.5% from ₹350 [NEAR 52W HIGH] +5pts</t>
         </is>
       </c>
       <c r="AU60" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AV60" t="inlineStr">
         <is>
-          <t>ATR-V: -17% compressed [EXPANDING]</t>
+          <t>ATR-V: -43% compressed [EXPANDING]</t>
         </is>
       </c>
       <c r="AW60" t="n">
@@ -30071,7 +30067,7 @@
         <v>0</v>
       </c>
       <c r="BA60" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BB60" t="inlineStr"/>
       <c r="BC60" t="n">
@@ -30092,25 +30088,25 @@
         </is>
       </c>
       <c r="BH60" t="n">
-        <v>121.73</v>
+        <v>299.96</v>
       </c>
       <c r="BI60" t="inlineStr">
         <is>
-          <t>Initial stop ₹121.73</t>
+          <t>Initial stop ₹299.96</t>
         </is>
       </c>
       <c r="BJ60" t="b">
         <v>0</v>
       </c>
       <c r="BK60" t="n">
-        <v>998</v>
+        <v>274</v>
       </c>
       <c r="BL60" t="n">
-        <v>128981.52</v>
+        <v>89666.5</v>
       </c>
       <c r="BM60" t="inlineStr">
         <is>
-          <t>998 shares · ₹128,982  (risk ₹7,500)</t>
+          <t>274 shares · ₹89,666  (risk ₹7,500)</t>
         </is>
       </c>
       <c r="BN60" t="n">
@@ -30125,11 +30121,11 @@
         </is>
       </c>
       <c r="BQ60" t="n">
-        <v>32</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="BR60" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 32.0% (t(df=4))</t>
+          <t>✅ MC survival 71.4% (500 sims, 20d, t(df=4))</t>
         </is>
       </c>
       <c r="BS60" t="inlineStr">
@@ -30163,19 +30159,19 @@
       </c>
       <c r="CB60" t="inlineStr"/>
       <c r="CC60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD60" t="n">
-        <v>7.47</v>
+        <v>20.82</v>
       </c>
       <c r="CE60" t="n">
-        <v>7.51</v>
+        <v>19.49</v>
       </c>
       <c r="CF60" t="n">
-        <v>1131450</v>
+        <v>218457</v>
       </c>
       <c r="CG60" t="n">
-        <v>139.22</v>
+        <v>296.42</v>
       </c>
       <c r="CH60" t="inlineStr">
         <is>
@@ -30184,7 +30180,7 @@
       </c>
       <c r="CI60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Institutional tide in — fii+dii both accumulating; recent filing: awarding of order(s)/contract(s) [sheets tab 4] | </t>
+          <t>Institutional tide in — fii+dii both accumulating; recent filing: analysts/institutional investor meet/con. call upd</t>
         </is>
       </c>
       <c r="CJ60" t="b">
@@ -30204,7 +30200,7 @@
         <v>0</v>
       </c>
       <c r="CP60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CQ60" t="b">
         <v>1</v>
@@ -30213,7 +30209,7 @@
         <v>0</v>
       </c>
       <c r="CS60" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="CT60" t="n">
         <v>0</v>
@@ -30236,7 +30232,7 @@
         <v>30</v>
       </c>
       <c r="CZ60" t="n">
-        <v>154.24</v>
+        <v>335.4</v>
       </c>
       <c r="DA60" t="b">
         <v>0</v>
@@ -30245,23 +30241,23 @@
         <v>0</v>
       </c>
       <c r="DC60" t="n">
-        <v>121.73</v>
+        <v>299.96</v>
       </c>
       <c r="DD60" t="n">
-        <v>121.73</v>
+        <v>299.96</v>
       </c>
       <c r="DE60" t="n">
-        <v>180.99</v>
+        <v>385.35</v>
       </c>
       <c r="DF60" t="n">
-        <v>222.75</v>
+        <v>474.27</v>
       </c>
       <c r="DG60" t="n">
-        <v>278.44</v>
+        <v>592.84</v>
       </c>
       <c r="DH60" t="inlineStr">
         <is>
-          <t>Sell 30% | Move stop to T1 ₹139.22</t>
+          <t>Sell 30% | Move stop to T1 ₹296.42</t>
         </is>
       </c>
       <c r="DI60" t="inlineStr">
@@ -30275,11 +30271,11 @@
         </is>
       </c>
       <c r="DK60" t="n">
-        <v>-7.2</v>
+        <v>10.4</v>
       </c>
       <c r="DL60" t="inlineStr">
         <is>
-          <t>👁️ WATCHING — score 30/100 · -7.2% vs T1</t>
+          <t>👁️ WATCHING — score 30/100 · +10.4% vs T1</t>
         </is>
       </c>
       <c r="DM60" t="inlineStr">
@@ -30321,7 +30317,7 @@
         <v>0</v>
       </c>
       <c r="DY60" t="n">
-        <v>15.02</v>
+        <v>38.98</v>
       </c>
       <c r="DZ60" t="inlineStr">
         <is>
@@ -30332,16 +30328,16 @@
         <v>1</v>
       </c>
       <c r="EB60" t="n">
-        <v>18.58</v>
+        <v>18.41</v>
       </c>
       <c r="EC60" t="n">
-        <v>0.01</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>TALBROAUTO</t>
+          <t>SCI</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -30350,26 +30346,26 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>327.25</v>
+        <v>326.9</v>
       </c>
       <c r="D61" t="n">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="E61" t="n">
         <v>200</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>🟠 MODERATE</t>
+          <t>🔵 PROBE</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>QTR 25%</t>
+          <t>PROBE 10%</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="I61" t="n">
         <v>30</v>
@@ -30378,43 +30374,43 @@
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="L61" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="M61" t="n">
-        <v>296.42</v>
+        <v>276.35</v>
       </c>
       <c r="N61" t="n">
-        <v>356.49</v>
+        <v>355.01</v>
       </c>
       <c r="O61" t="n">
-        <v>299.96</v>
+        <v>300.66</v>
       </c>
       <c r="P61" t="n">
-        <v>385.35</v>
+        <v>359.26</v>
       </c>
       <c r="Q61" t="n">
-        <v>474.27</v>
+        <v>442.16</v>
       </c>
       <c r="R61" t="n">
-        <v>592.84</v>
+        <v>552.7</v>
       </c>
       <c r="S61" t="n">
-        <v>8.34</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="T61" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="U61" t="n">
-        <v>85</v>
+        <v>80.7</v>
       </c>
       <c r="V61" t="n">
-        <v>57.9</v>
+        <v>59.9</v>
       </c>
       <c r="W61" t="n">
-        <v>63.8</v>
+        <v>48.2</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -30438,7 +30434,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>₹282.30–₹308.21</t>
+          <t>₹263.67–₹287.04</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
@@ -30450,7 +30446,7 @@
         <v>1.4</v>
       </c>
       <c r="AE61" t="n">
-        <v>17.8</v>
+        <v>36.7</v>
       </c>
       <c r="AF61" t="b">
         <v>0</v>
@@ -30465,7 +30461,7 @@
         <v>1</v>
       </c>
       <c r="AJ61" t="n">
-        <v>3.52</v>
+        <v>219.99</v>
       </c>
       <c r="AK61" t="inlineStr">
         <is>
@@ -30492,17 +30488,17 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>Analysts/institutional investor meet/con. call updates [SHEETS Tab 4]</t>
+          <t>Dividend [SHEETS Tab 4] | ⚠️ ROE(proxy) unverifiable — filing capped</t>
         </is>
       </c>
       <c r="AQ61" t="inlineStr">
         <is>
-          <t>⚠️ Results in 4td — risky, size to PROBE</t>
+          <t>No result date found (neutral)</t>
         </is>
       </c>
       <c r="AR61" t="inlineStr">
         <is>
-          <t>Not checked</t>
+          <t>ROE quality data unavailable</t>
         </is>
       </c>
       <c r="AS61" t="b">
@@ -30510,29 +30506,33 @@
       </c>
       <c r="AT61" t="inlineStr">
         <is>
-          <t>52W: 6.5% from ₹350 [NEAR 52W HIGH] +5pts</t>
+          <t>52W: 11.3% from ₹369 [APPROACHING HIGH] +3pts</t>
         </is>
       </c>
       <c r="AU61" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AV61" t="inlineStr">
         <is>
-          <t>ATR-V: -43% compressed [EXPANDING]</t>
+          <t>ATR-V: -35% compressed [EXPANDING]</t>
         </is>
       </c>
       <c r="AW61" t="n">
         <v>0</v>
       </c>
-      <c r="AX61" t="inlineStr"/>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>🔴 VDU 4-bar + price drop -3.6% — DISTRIBUTION (-3pts)</t>
+        </is>
+      </c>
       <c r="AY61" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="AZ61" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BA61" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BB61" t="inlineStr"/>
       <c r="BC61" t="n">
@@ -30553,25 +30553,25 @@
         </is>
       </c>
       <c r="BH61" t="n">
-        <v>299.96</v>
+        <v>300.66</v>
       </c>
       <c r="BI61" t="inlineStr">
         <is>
-          <t>Initial stop ₹299.96</t>
+          <t>Initial stop ₹300.66</t>
         </is>
       </c>
       <c r="BJ61" t="b">
         <v>0</v>
       </c>
       <c r="BK61" t="n">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="BL61" t="n">
-        <v>89666.5</v>
+        <v>93166.5</v>
       </c>
       <c r="BM61" t="inlineStr">
         <is>
-          <t>274 shares · ₹89,666  (risk ₹7,500)</t>
+          <t>285 shares · ₹93,166  (risk ₹7,500)</t>
         </is>
       </c>
       <c r="BN61" t="n">
@@ -30586,23 +30586,19 @@
         </is>
       </c>
       <c r="BQ61" t="n">
-        <v>72.40000000000001</v>
+        <v>69.2</v>
       </c>
       <c r="BR61" t="inlineStr">
         <is>
-          <t>✅ MC survival 72.4% (500 sims, 20d, t(df=4))</t>
+          <t>⚠️ MC survival 69.2% (t(df=4))</t>
         </is>
       </c>
       <c r="BS61" t="inlineStr">
         <is>
-          <t>ACCUMULATION</t>
-        </is>
-      </c>
-      <c r="BT61" t="inlineStr">
-        <is>
-          <t>🟢 CVD Accum — smart money</t>
-        </is>
-      </c>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="BT61" t="inlineStr"/>
       <c r="BU61" t="b">
         <v>0</v>
       </c>
@@ -30627,16 +30623,16 @@
         <v>0</v>
       </c>
       <c r="CD61" t="n">
-        <v>20.82</v>
+        <v>13.14</v>
       </c>
       <c r="CE61" t="n">
-        <v>19.49</v>
+        <v>18.74</v>
       </c>
       <c r="CF61" t="n">
-        <v>218457</v>
+        <v>18376034</v>
       </c>
       <c r="CG61" t="n">
-        <v>296.42</v>
+        <v>276.35</v>
       </c>
       <c r="CH61" t="inlineStr">
         <is>
@@ -30645,13 +30641,17 @@
       </c>
       <c r="CI61" t="inlineStr">
         <is>
-          <t>Institutional tide in — fii+dii both accumulating; recent filing: analysts/institutional investor meet/con. call upd</t>
+          <t>Institutional tide in — fii+dii both accumulating; recent filing: dividend [sheets tab 4] | ⚠️ roe(proxy) unverifiab</t>
         </is>
       </c>
       <c r="CJ61" t="b">
-        <v>0</v>
-      </c>
-      <c r="CK61" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="CK61" t="inlineStr">
+        <is>
+          <t>⚠️ ROUND_TRIP_RISK — close 327 &lt; 90% of 369</t>
+        </is>
+      </c>
       <c r="CL61" t="b">
         <v>0</v>
       </c>
@@ -30680,49 +30680,49 @@
         <v>0</v>
       </c>
       <c r="CU61" t="n">
-        <v>0.215</v>
+        <v>0.068</v>
       </c>
       <c r="CV61" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="CW61" t="n">
         <v>-5</v>
       </c>
       <c r="CX61" t="inlineStr">
         <is>
-          <t>🧠 Sniper Bayes 22% — LOW</t>
+          <t>🧠 Sniper Bayes 7% — LOW</t>
         </is>
       </c>
       <c r="CY61" t="n">
         <v>30</v>
       </c>
       <c r="CZ61" t="n">
-        <v>335.4</v>
+        <v>313.83</v>
       </c>
       <c r="DA61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DB61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DC61" t="n">
-        <v>299.96</v>
+        <v>300.66</v>
       </c>
       <c r="DD61" t="n">
-        <v>299.96</v>
+        <v>300.66</v>
       </c>
       <c r="DE61" t="n">
-        <v>385.35</v>
+        <v>359.26</v>
       </c>
       <c r="DF61" t="n">
-        <v>474.27</v>
+        <v>442.16</v>
       </c>
       <c r="DG61" t="n">
-        <v>592.84</v>
+        <v>552.7</v>
       </c>
       <c r="DH61" t="inlineStr">
         <is>
-          <t>Sell 30% | Move stop to T1 ₹296.42</t>
+          <t>Sell 30% | Move stop to T1 ₹276.35</t>
         </is>
       </c>
       <c r="DI61" t="inlineStr">
@@ -30736,11 +30736,11 @@
         </is>
       </c>
       <c r="DK61" t="n">
-        <v>10.4</v>
+        <v>18.3</v>
       </c>
       <c r="DL61" t="inlineStr">
         <is>
-          <t>👁️ WATCHING — score 30/100 · +10.4% vs T1</t>
+          <t>👁️ WATCHING — score 30/100 · +18.3% vs T1</t>
         </is>
       </c>
       <c r="DM61" t="inlineStr">
@@ -30782,7 +30782,7 @@
         <v>0</v>
       </c>
       <c r="DY61" t="n">
-        <v>38.98</v>
+        <v>37.48</v>
       </c>
       <c r="DZ61" t="inlineStr">
         <is>
@@ -30793,10 +30793,10 @@
         <v>1</v>
       </c>
       <c r="EB61" t="n">
-        <v>18.58</v>
+        <v>18.41</v>
       </c>
       <c r="EC61" t="n">
-        <v>0.01</v>
+        <v>0.45</v>
       </c>
     </row>
   </sheetData>
